--- a/Data Files/Backoffce/IndexacaoFG/Arquivos/Relatório de Recusas  04.08.2025 a 10.08.2025.xlsx
+++ b/Data Files/Backoffce/IndexacaoFG/Arquivos/Relatório de Recusas  04.08.2025 a 10.08.2025.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://allianzms.sharepoint.com/teams/BR0010-4356589/Shared Documents/BACK-OFFICE SME/Santander/2025/Relatório de Recusas/05. Maio/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F8A06A45-B4BB-4E96-ACB0-5E0421BF1705}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{2035410F-39B7-4362-9EAA-0009B0D0A2DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="19530" windowHeight="9780" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="19530" windowHeight="9780" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="04.08" sheetId="2" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="248" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="330" uniqueCount="84">
   <si>
     <t>SEGURADORA</t>
   </si>
@@ -195,13 +195,118 @@
   </si>
   <si>
     <t xml:space="preserve">GLAYCE APARECIDA ESPINULA                    </t>
+  </si>
+  <si>
+    <t>22 876 062 REGINALDO DA COSTA ME CNPJ 22876062000102</t>
+  </si>
+  <si>
+    <t>Chassi Irregular</t>
+  </si>
+  <si>
+    <t>R PANTOJA RODRIGUES LTDA ME CNPJ 38066386000107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JOSE ERNANDES PEREIRA DA SILVA               </t>
+  </si>
+  <si>
+    <t>Bônus;</t>
+  </si>
+  <si>
+    <t>Conforme CBE pela regra de mudança de cobertur
+a, da 2 para 1, ocorre a redução de 1 classe de bônus, assim sendo
+o correto bônus 0.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MARCIO FERNANDO RIBEIRO DA SILVA             </t>
+  </si>
+  <si>
+    <t>NUP Cancelamento 04.08.2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FELIPE DIEGO DE ARRUDA                       </t>
+  </si>
+  <si>
+    <t xml:space="preserve">SILVIA APARECIDA DE OLIVEIRA                 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">JULIO CESAR BUGMANN                          </t>
+  </si>
+  <si>
+    <t xml:space="preserve">E S ROCHA EPP                                </t>
+  </si>
+  <si>
+    <t xml:space="preserve">FELIPE SANTOS DUTRA                          </t>
+  </si>
+  <si>
+    <t xml:space="preserve">TOMAS BARBIERI                               </t>
+  </si>
+  <si>
+    <t xml:space="preserve">GISELY FRANCE ABRANTES                       </t>
+  </si>
+  <si>
+    <t>Para que possamos prosseguir
+coma liberação do bloqueio será necessário a apresentação do en
+dosso de cancelamento emitido</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KARINA CARLA DE ARAUJO COSTA                 </t>
+  </si>
+  <si>
+    <t>31 867 065 MARIA APARECIDA PINTO DE ARAUJO ME</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FRANCIELMA DE MESQUITA SOUSA MENDES          </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ROBERTO PONTES FERNANDES                     </t>
+  </si>
+  <si>
+    <t xml:space="preserve">THIAGO SABINO DE SOUZA                       </t>
+  </si>
+  <si>
+    <t xml:space="preserve">AMANDA MOLINA GARCIA DOS SANTOS              </t>
+  </si>
+  <si>
+    <t xml:space="preserve">CLAUDIA MARIA NASSIF ARRUDA DAVID            </t>
+  </si>
+  <si>
+    <t>Duplicidade;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	Santander - Veículo em duplicidade com proposta </t>
+  </si>
+  <si>
+    <t xml:space="preserve">MARIANGELA DE PAULA JUDICE                   </t>
+  </si>
+  <si>
+    <t>apólice anterior consta classe de
+bônus3, não havendo sinistro, conforme regra concede 1 classe de b
+ônus, assim sendo o correto bônus 4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JOAO DONIZETI CHIUZULI                       </t>
+  </si>
+  <si>
+    <t>***FRUSTRADO**CLIENTE NÃO CORRIGIU AS FOTOS INCORRETAS - PRAZO EXPIRADO FOTO INCORRETA: Foto 45º - Frente e Lateral Esquerda (Foto com placa obstruída, Foto com baixa iluminação). Foto 45º - Traseira e Lateral Direita (Foto com baixa iluminação).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ANDREZA FERNANDES DOS PASSOS DE PAULA        </t>
+  </si>
+  <si>
+    <t xml:space="preserve">VICTOR FERRER BORTONI                        </t>
+  </si>
+  <si>
+    <t xml:space="preserve">INOVA STEEL ESTRUTURAS METALICAS LTDA ME     </t>
+  </si>
+  <si>
+    <t xml:space="preserve">4TECH AUTOMACAO LTDA EPP                     </t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -245,6 +350,13 @@
       <family val="2"/>
       <charset val="1"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -260,7 +372,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="15">
+  <borders count="17">
     <border>
       <left/>
       <right/>
@@ -446,12 +558,38 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="54">
+  <cellXfs count="65">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -529,7 +667,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -581,13 +718,64 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal_Plan2_1" xfId="1" xr:uid="{69F13A52-20D9-46CA-8619-BC7A1BA09FD8}"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="2">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleMedium9"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -1056,7 +1244,7 @@
       <c r="E5" s="21">
         <v>3450043179</v>
       </c>
-      <c r="F5" s="50" t="s">
+      <c r="F5" s="49" t="s">
         <v>19</v>
       </c>
       <c r="G5" s="20" t="s">
@@ -1080,7 +1268,7 @@
       <c r="D6" s="25">
         <v>133632327</v>
       </c>
-      <c r="E6" s="48">
+      <c r="E6" s="47">
         <v>3450038405</v>
       </c>
       <c r="F6" s="12" t="s">
@@ -1109,7 +1297,7 @@
       <c r="D7" s="25">
         <v>133624469</v>
       </c>
-      <c r="E7" s="48">
+      <c r="E7" s="47">
         <v>3450037811</v>
       </c>
       <c r="F7" s="12" t="s">
@@ -1138,7 +1326,7 @@
       <c r="D8" s="25">
         <v>133625917</v>
       </c>
-      <c r="E8" s="48">
+      <c r="E8" s="47">
         <v>3450037910</v>
       </c>
       <c r="F8" s="12" t="s">
@@ -1167,7 +1355,7 @@
       <c r="D9" s="25">
         <v>133613919</v>
       </c>
-      <c r="E9" s="48">
+      <c r="E9" s="47">
         <v>3450037470</v>
       </c>
       <c r="F9" s="12" t="s">
@@ -1196,7 +1384,7 @@
       <c r="D10" s="25">
         <v>133630273</v>
       </c>
-      <c r="E10" s="48">
+      <c r="E10" s="47">
         <v>3450038207</v>
       </c>
       <c r="F10" s="12" t="s">
@@ -1225,7 +1413,7 @@
       <c r="D11" s="25">
         <v>133635781</v>
       </c>
-      <c r="E11" s="48">
+      <c r="E11" s="47">
         <v>3450038515</v>
       </c>
       <c r="F11" s="12" t="s">
@@ -1254,7 +1442,7 @@
       <c r="D12" s="25">
         <v>133664790</v>
       </c>
-      <c r="E12" s="48">
+      <c r="E12" s="47">
         <v>3450039736</v>
       </c>
       <c r="F12" s="12" t="s">
@@ -1283,7 +1471,7 @@
       <c r="D13" s="25">
         <v>133673295</v>
       </c>
-      <c r="E13" s="48">
+      <c r="E13" s="47">
         <v>3450040253</v>
       </c>
       <c r="F13" s="12" t="s">
@@ -1312,7 +1500,7 @@
       <c r="D14" s="25">
         <v>133659080</v>
       </c>
-      <c r="E14" s="48">
+      <c r="E14" s="47">
         <v>3450039241</v>
       </c>
       <c r="F14" s="12" t="s">
@@ -1341,7 +1529,7 @@
       <c r="D15" s="25">
         <v>133729067</v>
       </c>
-      <c r="E15" s="48">
+      <c r="E15" s="47">
         <v>3450042970</v>
       </c>
       <c r="F15" s="12" t="s">
@@ -1370,7 +1558,7 @@
       <c r="D16" s="25">
         <v>133649747</v>
       </c>
-      <c r="E16" s="48">
+      <c r="E16" s="47">
         <v>3450038966</v>
       </c>
       <c r="F16" s="12" t="s">
@@ -1399,7 +1587,7 @@
       <c r="D17" s="25">
         <v>133757334</v>
       </c>
-      <c r="E17" s="48">
+      <c r="E17" s="47">
         <v>3450044510</v>
       </c>
       <c r="F17" s="12" t="s">
@@ -1408,7 +1596,7 @@
       <c r="G17" s="20" t="s">
         <v>38</v>
       </c>
-      <c r="H17" s="53" t="s">
+      <c r="H17" s="9" t="s">
         <v>39</v>
       </c>
       <c r="I17" s="27">
@@ -1428,7 +1616,7 @@
       <c r="D18" s="25">
         <v>133613216</v>
       </c>
-      <c r="E18" s="48">
+      <c r="E18" s="47">
         <v>3450037437</v>
       </c>
       <c r="F18" s="12" t="s">
@@ -1457,7 +1645,7 @@
       <c r="D19" s="25">
         <v>133615484</v>
       </c>
-      <c r="E19" s="48">
+      <c r="E19" s="47">
         <v>3450037514</v>
       </c>
       <c r="F19" s="12" t="s">
@@ -1486,7 +1674,7 @@
       <c r="D20" s="25">
         <v>133627426</v>
       </c>
-      <c r="E20" s="48">
+      <c r="E20" s="47">
         <v>3450037976</v>
       </c>
       <c r="F20" s="12" t="s">
@@ -1515,7 +1703,7 @@
       <c r="D21" s="25">
         <v>133628230</v>
       </c>
-      <c r="E21" s="48">
+      <c r="E21" s="47">
         <v>3450038053</v>
       </c>
       <c r="F21" s="12" t="s">
@@ -1544,7 +1732,7 @@
       <c r="D22" s="25">
         <v>133629632</v>
       </c>
-      <c r="E22" s="48">
+      <c r="E22" s="47">
         <v>3450038141</v>
       </c>
       <c r="F22" s="12" t="s">
@@ -1573,7 +1761,7 @@
       <c r="D23" s="25">
         <v>133630563</v>
       </c>
-      <c r="E23" s="48">
+      <c r="E23" s="47">
         <v>3450038240</v>
       </c>
       <c r="F23" s="12" t="s">
@@ -1602,7 +1790,7 @@
       <c r="D24" s="25">
         <v>133630656</v>
       </c>
-      <c r="E24" s="48">
+      <c r="E24" s="47">
         <v>3450038273</v>
       </c>
       <c r="F24" s="12" t="s">
@@ -1631,7 +1819,7 @@
       <c r="D25" s="25">
         <v>133631738</v>
       </c>
-      <c r="E25" s="48">
+      <c r="E25" s="47">
         <v>3450038340</v>
       </c>
       <c r="F25" s="12" t="s">
@@ -1652,8 +1840,8 @@
       <c r="B26" s="7"/>
       <c r="C26" s="28"/>
       <c r="D26" s="25"/>
-      <c r="E26" s="49"/>
-      <c r="F26" s="51"/>
+      <c r="E26" s="48"/>
+      <c r="F26" s="50"/>
       <c r="G26" s="20"/>
       <c r="H26" s="9"/>
       <c r="I26" s="27"/>
@@ -1663,7 +1851,7 @@
       <c r="B27" s="7"/>
       <c r="C27" s="28"/>
       <c r="D27" s="25"/>
-      <c r="E27" s="49"/>
+      <c r="E27" s="48"/>
       <c r="F27" s="19"/>
       <c r="G27" s="20"/>
       <c r="H27" s="9"/>
@@ -1673,7 +1861,7 @@
       <c r="A28" s="6"/>
       <c r="B28" s="7"/>
       <c r="C28" s="7"/>
-      <c r="D28" s="52"/>
+      <c r="D28" s="51"/>
       <c r="E28" s="18"/>
       <c r="F28" s="19"/>
       <c r="G28" s="20"/>
@@ -1993,7 +2181,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FFA17127-7620-4DD9-9061-6C654E2EC5C2}">
-  <dimension ref="A1:I55"/>
+  <dimension ref="A1:I52"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
@@ -2002,7 +2190,7 @@
     <col min="4" max="4" width="27.7109375" style="17" customWidth="1"/>
     <col min="5" max="5" width="18.5703125" customWidth="1"/>
     <col min="6" max="6" width="31.5703125" customWidth="1"/>
-    <col min="7" max="7" width="19.7109375" customWidth="1"/>
+    <col min="7" max="7" width="19.7109375" style="63" customWidth="1"/>
     <col min="8" max="8" width="24" customWidth="1"/>
     <col min="9" max="9" width="22.7109375" style="16" customWidth="1"/>
   </cols>
@@ -2040,307 +2228,703 @@
       <c r="A2" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="7"/>
-      <c r="C2" s="28"/>
-      <c r="D2" s="25"/>
-      <c r="E2" s="18"/>
-      <c r="F2" s="12"/>
-      <c r="G2" s="20"/>
-      <c r="H2" s="12"/>
+      <c r="B2" s="7">
+        <v>45870</v>
+      </c>
+      <c r="C2" s="28">
+        <v>45874</v>
+      </c>
+      <c r="D2" s="25" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2" s="58">
+        <v>3450042651</v>
+      </c>
+      <c r="F2" s="12" t="s">
+        <v>51</v>
+      </c>
+      <c r="G2" s="60" t="s">
+        <v>16</v>
+      </c>
+      <c r="H2" s="12" t="s">
+        <v>52</v>
+      </c>
       <c r="I2" s="27"/>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="7"/>
-      <c r="C3" s="28"/>
-      <c r="D3" s="25"/>
-      <c r="E3" s="18"/>
-      <c r="F3" s="12"/>
-      <c r="G3" s="20"/>
-      <c r="H3" s="9"/>
+      <c r="B3" s="7">
+        <v>45873</v>
+      </c>
+      <c r="C3" s="28">
+        <v>45874</v>
+      </c>
+      <c r="D3" s="57" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3" s="58">
+        <v>3450044037</v>
+      </c>
+      <c r="F3" s="12" t="s">
+        <v>53</v>
+      </c>
+      <c r="G3" s="60" t="s">
+        <v>16</v>
+      </c>
+      <c r="H3" s="12" t="s">
+        <v>52</v>
+      </c>
       <c r="I3" s="27"/>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="7"/>
-      <c r="C4" s="28"/>
-      <c r="D4" s="25"/>
-      <c r="E4" s="18"/>
-      <c r="F4" s="12"/>
-      <c r="G4" s="20"/>
-      <c r="H4" s="9"/>
-      <c r="I4" s="27"/>
+      <c r="B4" s="7">
+        <v>45868</v>
+      </c>
+      <c r="C4" s="28">
+        <v>45874</v>
+      </c>
+      <c r="D4" s="55">
+        <v>133569706</v>
+      </c>
+      <c r="E4" s="56">
+        <v>3450035633</v>
+      </c>
+      <c r="F4" s="52" t="s">
+        <v>54</v>
+      </c>
+      <c r="G4" s="60" t="s">
+        <v>55</v>
+      </c>
+      <c r="H4" s="59" t="s">
+        <v>56</v>
+      </c>
+      <c r="I4" s="27">
+        <v>45866</v>
+      </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="7"/>
-      <c r="C5" s="28"/>
-      <c r="D5" s="25"/>
-      <c r="E5" s="18"/>
-      <c r="F5" s="12"/>
-      <c r="G5" s="20"/>
-      <c r="H5" s="9"/>
-      <c r="I5" s="27"/>
+      <c r="B5" s="7">
+        <v>45872</v>
+      </c>
+      <c r="C5" s="28">
+        <v>45874</v>
+      </c>
+      <c r="D5" s="55">
+        <v>133653803</v>
+      </c>
+      <c r="E5" s="48">
+        <v>3450039164</v>
+      </c>
+      <c r="F5" s="53" t="s">
+        <v>57</v>
+      </c>
+      <c r="G5" s="60" t="s">
+        <v>13</v>
+      </c>
+      <c r="H5" s="59" t="s">
+        <v>58</v>
+      </c>
+      <c r="I5" s="27">
+        <v>45873</v>
+      </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="7"/>
-      <c r="C6" s="28"/>
-      <c r="D6" s="25"/>
-      <c r="E6" s="18"/>
-      <c r="F6" s="12"/>
-      <c r="G6" s="20"/>
-      <c r="H6" s="22"/>
-      <c r="I6" s="27"/>
+      <c r="B6" s="7">
+        <v>45863</v>
+      </c>
+      <c r="C6" s="28">
+        <v>45874</v>
+      </c>
+      <c r="D6" s="55">
+        <v>133639832</v>
+      </c>
+      <c r="E6" s="48">
+        <v>3450038438</v>
+      </c>
+      <c r="F6" s="53" t="s">
+        <v>59</v>
+      </c>
+      <c r="G6" s="60" t="s">
+        <v>21</v>
+      </c>
+      <c r="H6" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="I6" s="27">
+        <v>45863</v>
+      </c>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B7" s="7"/>
-      <c r="C7" s="28"/>
-      <c r="D7" s="25"/>
-      <c r="E7" s="18"/>
-      <c r="F7" s="12"/>
-      <c r="G7" s="26"/>
-      <c r="H7" s="31"/>
-      <c r="I7" s="27"/>
+      <c r="B7" s="7">
+        <v>45860</v>
+      </c>
+      <c r="C7" s="28">
+        <v>45874</v>
+      </c>
+      <c r="D7" s="55">
+        <v>133636937</v>
+      </c>
+      <c r="E7" s="48">
+        <v>3450034885</v>
+      </c>
+      <c r="F7" s="53" t="s">
+        <v>60</v>
+      </c>
+      <c r="G7" s="61" t="s">
+        <v>21</v>
+      </c>
+      <c r="H7" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="I7" s="27">
+        <v>45860</v>
+      </c>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B8" s="7"/>
-      <c r="C8" s="28"/>
-      <c r="D8" s="25"/>
-      <c r="E8" s="18"/>
-      <c r="F8" s="12"/>
-      <c r="G8" s="26"/>
-      <c r="H8" s="12"/>
-      <c r="I8" s="27"/>
+      <c r="B8" s="7">
+        <v>45860</v>
+      </c>
+      <c r="C8" s="28">
+        <v>45874</v>
+      </c>
+      <c r="D8" s="55">
+        <v>133636970</v>
+      </c>
+      <c r="E8" s="48">
+        <v>3450034742</v>
+      </c>
+      <c r="F8" s="53" t="s">
+        <v>61</v>
+      </c>
+      <c r="G8" s="61" t="s">
+        <v>21</v>
+      </c>
+      <c r="H8" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="I8" s="27">
+        <v>45860</v>
+      </c>
     </row>
     <row r="9" spans="1:9">
       <c r="A9" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B9" s="7"/>
-      <c r="C9" s="28"/>
-      <c r="D9" s="25"/>
-      <c r="E9" s="18"/>
-      <c r="F9" s="12"/>
-      <c r="G9" s="20"/>
-      <c r="H9" s="15"/>
-      <c r="I9" s="27"/>
+      <c r="B9" s="7">
+        <v>45867</v>
+      </c>
+      <c r="C9" s="28">
+        <v>45874</v>
+      </c>
+      <c r="D9" s="55">
+        <v>133668500</v>
+      </c>
+      <c r="E9" s="48">
+        <v>3450039934</v>
+      </c>
+      <c r="F9" s="53" t="s">
+        <v>62</v>
+      </c>
+      <c r="G9" s="60" t="s">
+        <v>24</v>
+      </c>
+      <c r="H9" s="64" t="s">
+        <v>41</v>
+      </c>
+      <c r="I9" s="27">
+        <v>45867</v>
+      </c>
     </row>
     <row r="10" spans="1:9">
       <c r="A10" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B10" s="7"/>
-      <c r="C10" s="28"/>
-      <c r="D10" s="25"/>
-      <c r="E10" s="18"/>
-      <c r="F10" s="12"/>
-      <c r="G10" s="20"/>
-      <c r="H10" s="9"/>
-      <c r="I10" s="27"/>
+      <c r="B10" s="7">
+        <v>45868</v>
+      </c>
+      <c r="C10" s="28">
+        <v>45874</v>
+      </c>
+      <c r="D10" s="55">
+        <v>133692443</v>
+      </c>
+      <c r="E10" s="48">
+        <v>3450041090</v>
+      </c>
+      <c r="F10" s="53" t="s">
+        <v>63</v>
+      </c>
+      <c r="G10" s="60" t="s">
+        <v>13</v>
+      </c>
+      <c r="H10" s="59" t="s">
+        <v>58</v>
+      </c>
+      <c r="I10" s="27">
+        <v>45873</v>
+      </c>
     </row>
     <row r="11" spans="1:9">
       <c r="A11" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B11" s="7"/>
-      <c r="C11" s="28"/>
-      <c r="D11" s="25"/>
-      <c r="E11" s="18"/>
-      <c r="F11" s="12"/>
-      <c r="G11" s="20"/>
-      <c r="H11" s="9"/>
-      <c r="I11" s="27"/>
+      <c r="B11" s="7">
+        <v>45867</v>
+      </c>
+      <c r="C11" s="28">
+        <v>45874</v>
+      </c>
+      <c r="D11" s="55">
+        <v>133669604</v>
+      </c>
+      <c r="E11" s="48">
+        <v>3450040066</v>
+      </c>
+      <c r="F11" s="53" t="s">
+        <v>64</v>
+      </c>
+      <c r="G11" s="60" t="s">
+        <v>38</v>
+      </c>
+      <c r="H11" s="59" t="s">
+        <v>39</v>
+      </c>
+      <c r="I11" s="27">
+        <v>45867</v>
+      </c>
     </row>
     <row r="12" spans="1:9">
       <c r="A12" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B12" s="7"/>
-      <c r="C12" s="28"/>
-      <c r="D12" s="25"/>
-      <c r="E12" s="18"/>
-      <c r="F12" s="12"/>
-      <c r="G12" s="20"/>
-      <c r="H12" s="9"/>
-      <c r="I12" s="27"/>
+      <c r="B12" s="7">
+        <v>45891</v>
+      </c>
+      <c r="C12" s="28">
+        <v>45874</v>
+      </c>
+      <c r="D12" s="55">
+        <v>133577309</v>
+      </c>
+      <c r="E12" s="48">
+        <v>3450036007</v>
+      </c>
+      <c r="F12" s="53" t="s">
+        <v>65</v>
+      </c>
+      <c r="G12" s="60" t="s">
+        <v>55</v>
+      </c>
+      <c r="H12" s="59" t="s">
+        <v>66</v>
+      </c>
+      <c r="I12" s="27">
+        <v>45863</v>
+      </c>
     </row>
     <row r="13" spans="1:9">
       <c r="A13" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B13" s="7"/>
-      <c r="C13" s="28"/>
-      <c r="D13" s="25"/>
-      <c r="E13" s="18"/>
-      <c r="F13" s="12"/>
-      <c r="G13" s="20"/>
-      <c r="H13" s="9"/>
-      <c r="I13" s="27"/>
+      <c r="B13" s="7">
+        <v>45869</v>
+      </c>
+      <c r="C13" s="28">
+        <v>45874</v>
+      </c>
+      <c r="D13" s="55">
+        <v>133708632</v>
+      </c>
+      <c r="E13" s="48">
+        <v>3450041738</v>
+      </c>
+      <c r="F13" s="53" t="s">
+        <v>67</v>
+      </c>
+      <c r="G13" s="60" t="s">
+        <v>38</v>
+      </c>
+      <c r="H13" s="59" t="s">
+        <v>39</v>
+      </c>
+      <c r="I13" s="27">
+        <v>45869</v>
+      </c>
     </row>
     <row r="14" spans="1:9">
       <c r="A14" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B14" s="7"/>
-      <c r="C14" s="28"/>
-      <c r="D14" s="25"/>
-      <c r="E14" s="18"/>
-      <c r="F14" s="12"/>
-      <c r="G14" s="20"/>
-      <c r="H14" s="9"/>
-      <c r="I14" s="27"/>
+      <c r="B14" s="7">
+        <v>45870</v>
+      </c>
+      <c r="C14" s="28">
+        <v>45874</v>
+      </c>
+      <c r="D14" s="55">
+        <v>133723098</v>
+      </c>
+      <c r="E14" s="48">
+        <v>3450042475</v>
+      </c>
+      <c r="F14" s="53" t="s">
+        <v>68</v>
+      </c>
+      <c r="G14" s="60" t="s">
+        <v>38</v>
+      </c>
+      <c r="H14" s="59" t="s">
+        <v>39</v>
+      </c>
+      <c r="I14" s="27">
+        <v>45870</v>
+      </c>
     </row>
     <row r="15" spans="1:9">
       <c r="A15" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B15" s="7"/>
-      <c r="C15" s="28"/>
-      <c r="D15" s="25"/>
-      <c r="E15" s="18"/>
-      <c r="F15" s="12"/>
-      <c r="G15" s="20"/>
-      <c r="H15" s="9"/>
-      <c r="I15" s="27"/>
+      <c r="B15" s="7">
+        <v>45870</v>
+      </c>
+      <c r="C15" s="28">
+        <v>45874</v>
+      </c>
+      <c r="D15" s="55">
+        <v>133738294</v>
+      </c>
+      <c r="E15" s="48">
+        <v>3450043553</v>
+      </c>
+      <c r="F15" s="53" t="s">
+        <v>69</v>
+      </c>
+      <c r="G15" s="60" t="s">
+        <v>13</v>
+      </c>
+      <c r="H15" s="59" t="s">
+        <v>58</v>
+      </c>
+      <c r="I15" s="27">
+        <v>45873</v>
+      </c>
     </row>
     <row r="16" spans="1:9">
       <c r="A16" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B16" s="7"/>
-      <c r="C16" s="28"/>
-      <c r="D16" s="25"/>
-      <c r="E16" s="18"/>
-      <c r="F16" s="12"/>
-      <c r="G16" s="20"/>
-      <c r="H16" s="9"/>
-      <c r="I16" s="27"/>
+      <c r="B16" s="7">
+        <v>45899</v>
+      </c>
+      <c r="C16" s="28">
+        <v>45874</v>
+      </c>
+      <c r="D16" s="55">
+        <v>133732110</v>
+      </c>
+      <c r="E16" s="48">
+        <v>3450043135</v>
+      </c>
+      <c r="F16" s="53" t="s">
+        <v>70</v>
+      </c>
+      <c r="G16" s="60" t="s">
+        <v>13</v>
+      </c>
+      <c r="H16" s="59" t="s">
+        <v>58</v>
+      </c>
+      <c r="I16" s="27">
+        <v>45873</v>
+      </c>
     </row>
     <row r="17" spans="1:9">
       <c r="A17" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B17" s="7"/>
-      <c r="C17" s="28"/>
-      <c r="D17" s="25"/>
-      <c r="E17" s="18"/>
-      <c r="F17" s="12"/>
-      <c r="G17" s="20"/>
-      <c r="H17" s="9"/>
-      <c r="I17" s="27"/>
+      <c r="B17" s="7">
+        <v>45870</v>
+      </c>
+      <c r="C17" s="28">
+        <v>45874</v>
+      </c>
+      <c r="D17" s="55">
+        <v>133722984</v>
+      </c>
+      <c r="E17" s="48">
+        <v>3450042464</v>
+      </c>
+      <c r="F17" s="53" t="s">
+        <v>71</v>
+      </c>
+      <c r="G17" s="60" t="s">
+        <v>13</v>
+      </c>
+      <c r="H17" s="59" t="s">
+        <v>58</v>
+      </c>
+      <c r="I17" s="27">
+        <v>45873</v>
+      </c>
     </row>
     <row r="18" spans="1:9">
-      <c r="A18" s="6"/>
-      <c r="B18" s="7"/>
-      <c r="C18" s="28"/>
-      <c r="D18" s="25"/>
-      <c r="E18" s="18"/>
-      <c r="F18" s="12"/>
-      <c r="G18" s="20"/>
-      <c r="H18" s="9"/>
-      <c r="I18" s="27"/>
+      <c r="A18" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B18" s="7">
+        <v>45873</v>
+      </c>
+      <c r="C18" s="28">
+        <v>45874</v>
+      </c>
+      <c r="D18" s="55">
+        <v>133762552</v>
+      </c>
+      <c r="E18" s="48">
+        <v>3450044884</v>
+      </c>
+      <c r="F18" s="53" t="s">
+        <v>72</v>
+      </c>
+      <c r="G18" s="60" t="s">
+        <v>21</v>
+      </c>
+      <c r="H18" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="I18" s="27">
+        <v>45873</v>
+      </c>
     </row>
     <row r="19" spans="1:9">
-      <c r="A19" s="6"/>
-      <c r="B19" s="7"/>
-      <c r="C19" s="28"/>
-      <c r="D19" s="25"/>
-      <c r="E19" s="18"/>
-      <c r="F19" s="12"/>
-      <c r="G19" s="20"/>
-      <c r="H19" s="9"/>
-      <c r="I19" s="27"/>
+      <c r="A19" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B19" s="7">
+        <v>45863</v>
+      </c>
+      <c r="C19" s="28">
+        <v>45874</v>
+      </c>
+      <c r="D19" s="55">
+        <v>133572143</v>
+      </c>
+      <c r="E19" s="48">
+        <v>3450035721</v>
+      </c>
+      <c r="F19" s="53" t="s">
+        <v>73</v>
+      </c>
+      <c r="G19" s="60" t="s">
+        <v>74</v>
+      </c>
+      <c r="H19" s="59" t="s">
+        <v>75</v>
+      </c>
+      <c r="I19" s="27">
+        <v>45863</v>
+      </c>
     </row>
     <row r="20" spans="1:9">
-      <c r="A20" s="6"/>
-      <c r="B20" s="7"/>
-      <c r="C20" s="28"/>
-      <c r="D20" s="25"/>
-      <c r="E20" s="18"/>
-      <c r="F20" s="12"/>
-      <c r="G20" s="20"/>
-      <c r="H20" s="9"/>
-      <c r="I20" s="27"/>
+      <c r="A20" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B20" s="7">
+        <v>45882</v>
+      </c>
+      <c r="C20" s="28">
+        <v>45874</v>
+      </c>
+      <c r="D20" s="55">
+        <v>133587069</v>
+      </c>
+      <c r="E20" s="48">
+        <v>3450036370</v>
+      </c>
+      <c r="F20" s="53" t="s">
+        <v>76</v>
+      </c>
+      <c r="G20" s="60" t="s">
+        <v>55</v>
+      </c>
+      <c r="H20" s="59" t="s">
+        <v>77</v>
+      </c>
+      <c r="I20" s="27">
+        <v>45863</v>
+      </c>
     </row>
     <row r="21" spans="1:9">
-      <c r="A21" s="6"/>
-      <c r="B21" s="7"/>
-      <c r="C21" s="28"/>
-      <c r="D21" s="25"/>
-      <c r="E21" s="18"/>
-      <c r="F21" s="12"/>
-      <c r="G21" s="20"/>
-      <c r="H21" s="9"/>
-      <c r="I21" s="27"/>
+      <c r="A21" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B21" s="7">
+        <v>45867</v>
+      </c>
+      <c r="C21" s="28">
+        <v>45874</v>
+      </c>
+      <c r="D21" s="55">
+        <v>133673079</v>
+      </c>
+      <c r="E21" s="48">
+        <v>3450040242</v>
+      </c>
+      <c r="F21" s="53" t="s">
+        <v>78</v>
+      </c>
+      <c r="G21" s="60" t="s">
+        <v>24</v>
+      </c>
+      <c r="H21" s="59" t="s">
+        <v>79</v>
+      </c>
+      <c r="I21" s="27">
+        <v>45867</v>
+      </c>
     </row>
     <row r="22" spans="1:9">
-      <c r="A22" s="6"/>
-      <c r="B22" s="7"/>
-      <c r="C22" s="28"/>
-      <c r="D22" s="25"/>
-      <c r="E22" s="18"/>
-      <c r="F22" s="12"/>
-      <c r="G22" s="20"/>
-      <c r="H22" s="9"/>
-      <c r="I22" s="27"/>
+      <c r="A22" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B22" s="7">
+        <v>45884</v>
+      </c>
+      <c r="C22" s="28">
+        <v>45874</v>
+      </c>
+      <c r="D22" s="55">
+        <v>133664733</v>
+      </c>
+      <c r="E22" s="48">
+        <v>3450039725</v>
+      </c>
+      <c r="F22" s="53" t="s">
+        <v>80</v>
+      </c>
+      <c r="G22" s="60" t="s">
+        <v>13</v>
+      </c>
+      <c r="H22" s="59" t="s">
+        <v>58</v>
+      </c>
+      <c r="I22" s="27">
+        <v>45873</v>
+      </c>
     </row>
     <row r="23" spans="1:9">
-      <c r="A23" s="6"/>
-      <c r="B23" s="7"/>
-      <c r="C23" s="28"/>
-      <c r="D23" s="25"/>
-      <c r="E23" s="18"/>
-      <c r="F23" s="12"/>
-      <c r="G23" s="20"/>
-      <c r="H23" s="9"/>
-      <c r="I23" s="27"/>
+      <c r="A23" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B23" s="7">
+        <v>45865</v>
+      </c>
+      <c r="C23" s="28">
+        <v>45874</v>
+      </c>
+      <c r="D23" s="55">
+        <v>133637794</v>
+      </c>
+      <c r="E23" s="48">
+        <v>3450038537</v>
+      </c>
+      <c r="F23" s="53" t="s">
+        <v>81</v>
+      </c>
+      <c r="G23" s="60" t="s">
+        <v>21</v>
+      </c>
+      <c r="H23" s="31" t="s">
+        <v>22</v>
+      </c>
+      <c r="I23" s="27">
+        <v>45865</v>
+      </c>
     </row>
     <row r="24" spans="1:9">
-      <c r="A24" s="6"/>
-      <c r="B24" s="7"/>
-      <c r="C24" s="28"/>
-      <c r="D24" s="25"/>
-      <c r="E24" s="18"/>
-      <c r="F24" s="12"/>
-      <c r="G24" s="20"/>
-      <c r="H24" s="9"/>
-      <c r="I24" s="27"/>
+      <c r="A24" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B24" s="7">
+        <v>45866</v>
+      </c>
+      <c r="C24" s="28">
+        <v>45874</v>
+      </c>
+      <c r="D24" s="55">
+        <v>133653367</v>
+      </c>
+      <c r="E24" s="48">
+        <v>3450039131</v>
+      </c>
+      <c r="F24" s="53" t="s">
+        <v>82</v>
+      </c>
+      <c r="G24" s="60" t="s">
+        <v>21</v>
+      </c>
+      <c r="H24" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="I24" s="27">
+        <v>45866</v>
+      </c>
     </row>
     <row r="25" spans="1:9">
-      <c r="A25" s="6"/>
-      <c r="B25" s="7"/>
-      <c r="C25" s="28"/>
-      <c r="D25" s="25"/>
-      <c r="E25" s="18"/>
-      <c r="F25" s="12"/>
-      <c r="G25" s="20"/>
-      <c r="H25" s="9"/>
-      <c r="I25" s="27"/>
+      <c r="A25" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B25" s="7">
+        <v>45866</v>
+      </c>
+      <c r="C25" s="28">
+        <v>45874</v>
+      </c>
+      <c r="D25" s="55">
+        <v>133653584</v>
+      </c>
+      <c r="E25" s="48">
+        <v>3450039153</v>
+      </c>
+      <c r="F25" s="53" t="s">
+        <v>83</v>
+      </c>
+      <c r="G25" s="60" t="s">
+        <v>21</v>
+      </c>
+      <c r="H25" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="I25" s="27">
+        <v>45866</v>
+      </c>
     </row>
     <row r="26" spans="1:9">
       <c r="A26" s="6"/>
       <c r="B26" s="7"/>
       <c r="C26" s="28"/>
-      <c r="D26" s="25"/>
-      <c r="E26" s="18"/>
-      <c r="F26" s="12"/>
-      <c r="G26" s="20"/>
-      <c r="H26" s="32"/>
+      <c r="D26" s="51"/>
+      <c r="E26" s="54"/>
+      <c r="F26" s="35"/>
+      <c r="G26" s="60"/>
+      <c r="H26" s="9"/>
       <c r="I26" s="27"/>
     </row>
     <row r="27" spans="1:9">
@@ -2350,7 +2934,7 @@
       <c r="D27" s="25"/>
       <c r="E27" s="18"/>
       <c r="F27" s="12"/>
-      <c r="G27" s="20"/>
+      <c r="G27" s="60"/>
       <c r="H27" s="9"/>
       <c r="I27" s="27"/>
     </row>
@@ -2361,7 +2945,7 @@
       <c r="D28" s="25"/>
       <c r="E28" s="18"/>
       <c r="F28" s="12"/>
-      <c r="G28" s="20"/>
+      <c r="G28" s="60"/>
       <c r="H28" s="9"/>
       <c r="I28" s="27"/>
     </row>
@@ -2372,7 +2956,7 @@
       <c r="D29" s="25"/>
       <c r="E29" s="18"/>
       <c r="F29" s="12"/>
-      <c r="G29" s="20"/>
+      <c r="G29" s="60"/>
       <c r="H29" s="9"/>
       <c r="I29" s="27"/>
     </row>
@@ -2383,40 +2967,40 @@
       <c r="D30" s="25"/>
       <c r="E30" s="18"/>
       <c r="F30" s="12"/>
-      <c r="G30" s="20"/>
+      <c r="G30" s="60"/>
       <c r="H30" s="9"/>
       <c r="I30" s="27"/>
     </row>
     <row r="31" spans="1:9">
       <c r="A31" s="6"/>
-      <c r="B31" s="7"/>
-      <c r="C31" s="28"/>
-      <c r="D31" s="25"/>
-      <c r="E31" s="18"/>
-      <c r="F31" s="12"/>
-      <c r="G31" s="20"/>
+      <c r="B31" s="8"/>
+      <c r="C31" s="7"/>
+      <c r="D31" s="23"/>
+      <c r="E31" s="23"/>
+      <c r="F31" s="15"/>
+      <c r="G31" s="62"/>
       <c r="H31" s="9"/>
       <c r="I31" s="27"/>
     </row>
     <row r="32" spans="1:9">
       <c r="A32" s="6"/>
-      <c r="B32" s="7"/>
-      <c r="C32" s="28"/>
-      <c r="D32" s="25"/>
-      <c r="E32" s="18"/>
-      <c r="F32" s="12"/>
-      <c r="G32" s="20"/>
+      <c r="B32" s="8"/>
+      <c r="C32" s="7"/>
+      <c r="D32" s="8"/>
+      <c r="E32" s="8"/>
+      <c r="F32" s="9"/>
+      <c r="G32" s="62"/>
       <c r="H32" s="9"/>
       <c r="I32" s="27"/>
     </row>
     <row r="33" spans="1:9">
       <c r="A33" s="6"/>
-      <c r="B33" s="7"/>
-      <c r="C33" s="28"/>
-      <c r="D33" s="25"/>
-      <c r="E33" s="18"/>
-      <c r="F33" s="12"/>
-      <c r="G33" s="20"/>
+      <c r="B33" s="8"/>
+      <c r="C33" s="7"/>
+      <c r="D33" s="8"/>
+      <c r="E33" s="8"/>
+      <c r="F33" s="9"/>
+      <c r="G33" s="62"/>
       <c r="H33" s="9"/>
       <c r="I33" s="27"/>
     </row>
@@ -2424,12 +3008,12 @@
       <c r="A34" s="6"/>
       <c r="B34" s="8"/>
       <c r="C34" s="7"/>
-      <c r="D34" s="23"/>
-      <c r="E34" s="23"/>
-      <c r="F34" s="15"/>
-      <c r="G34" s="6"/>
+      <c r="D34" s="8"/>
+      <c r="E34" s="8"/>
+      <c r="F34" s="9"/>
+      <c r="G34" s="62"/>
       <c r="H34" s="9"/>
-      <c r="I34" s="27"/>
+      <c r="I34"/>
     </row>
     <row r="35" spans="1:9">
       <c r="A35" s="6"/>
@@ -2438,9 +3022,9 @@
       <c r="D35" s="8"/>
       <c r="E35" s="8"/>
       <c r="F35" s="9"/>
-      <c r="G35" s="6"/>
+      <c r="G35" s="62"/>
       <c r="H35" s="9"/>
-      <c r="I35" s="27"/>
+      <c r="I35"/>
     </row>
     <row r="36" spans="1:9">
       <c r="A36" s="6"/>
@@ -2449,9 +3033,9 @@
       <c r="D36" s="8"/>
       <c r="E36" s="8"/>
       <c r="F36" s="9"/>
-      <c r="G36" s="6"/>
+      <c r="G36" s="62"/>
       <c r="H36" s="9"/>
-      <c r="I36" s="27"/>
+      <c r="I36"/>
     </row>
     <row r="37" spans="1:9">
       <c r="A37" s="6"/>
@@ -2460,7 +3044,7 @@
       <c r="D37" s="8"/>
       <c r="E37" s="8"/>
       <c r="F37" s="9"/>
-      <c r="G37" s="6"/>
+      <c r="G37" s="62"/>
       <c r="H37" s="9"/>
       <c r="I37"/>
     </row>
@@ -2471,7 +3055,7 @@
       <c r="D38" s="8"/>
       <c r="E38" s="8"/>
       <c r="F38" s="9"/>
-      <c r="G38" s="6"/>
+      <c r="G38" s="62"/>
       <c r="H38" s="9"/>
       <c r="I38"/>
     </row>
@@ -2482,7 +3066,7 @@
       <c r="D39" s="8"/>
       <c r="E39" s="8"/>
       <c r="F39" s="9"/>
-      <c r="G39" s="6"/>
+      <c r="G39" s="62"/>
       <c r="H39" s="9"/>
       <c r="I39"/>
     </row>
@@ -2493,7 +3077,7 @@
       <c r="D40" s="8"/>
       <c r="E40" s="8"/>
       <c r="F40" s="9"/>
-      <c r="G40" s="6"/>
+      <c r="G40" s="62"/>
       <c r="H40" s="9"/>
       <c r="I40"/>
     </row>
@@ -2504,7 +3088,7 @@
       <c r="D41" s="8"/>
       <c r="E41" s="8"/>
       <c r="F41" s="9"/>
-      <c r="G41" s="6"/>
+      <c r="G41" s="62"/>
       <c r="H41" s="9"/>
       <c r="I41"/>
     </row>
@@ -2515,7 +3099,7 @@
       <c r="D42" s="8"/>
       <c r="E42" s="8"/>
       <c r="F42" s="9"/>
-      <c r="G42" s="6"/>
+      <c r="G42" s="62"/>
       <c r="H42" s="9"/>
       <c r="I42"/>
     </row>
@@ -2526,7 +3110,7 @@
       <c r="D43" s="8"/>
       <c r="E43" s="8"/>
       <c r="F43" s="9"/>
-      <c r="G43" s="6"/>
+      <c r="G43" s="62"/>
       <c r="H43" s="9"/>
       <c r="I43"/>
     </row>
@@ -2537,7 +3121,7 @@
       <c r="D44" s="8"/>
       <c r="E44" s="8"/>
       <c r="F44" s="9"/>
-      <c r="G44" s="6"/>
+      <c r="G44" s="62"/>
       <c r="H44" s="9"/>
       <c r="I44"/>
     </row>
@@ -2548,7 +3132,7 @@
       <c r="D45" s="8"/>
       <c r="E45" s="8"/>
       <c r="F45" s="9"/>
-      <c r="G45" s="6"/>
+      <c r="G45" s="62"/>
       <c r="H45" s="9"/>
       <c r="I45"/>
     </row>
@@ -2559,7 +3143,7 @@
       <c r="D46" s="8"/>
       <c r="E46" s="8"/>
       <c r="F46" s="9"/>
-      <c r="G46" s="6"/>
+      <c r="G46" s="62"/>
       <c r="H46" s="9"/>
       <c r="I46"/>
     </row>
@@ -2570,7 +3154,7 @@
       <c r="D47" s="8"/>
       <c r="E47" s="8"/>
       <c r="F47" s="9"/>
-      <c r="G47" s="6"/>
+      <c r="G47" s="62"/>
       <c r="H47" s="9"/>
       <c r="I47"/>
     </row>
@@ -2581,7 +3165,7 @@
       <c r="D48" s="8"/>
       <c r="E48" s="8"/>
       <c r="F48" s="9"/>
-      <c r="G48" s="6"/>
+      <c r="G48" s="62"/>
       <c r="H48" s="9"/>
       <c r="I48"/>
     </row>
@@ -2592,7 +3176,7 @@
       <c r="D49" s="8"/>
       <c r="E49" s="8"/>
       <c r="F49" s="9"/>
-      <c r="G49" s="6"/>
+      <c r="G49" s="62"/>
       <c r="H49" s="9"/>
       <c r="I49"/>
     </row>
@@ -2603,7 +3187,7 @@
       <c r="D50" s="8"/>
       <c r="E50" s="8"/>
       <c r="F50" s="9"/>
-      <c r="G50" s="6"/>
+      <c r="G50" s="62"/>
       <c r="H50" s="9"/>
       <c r="I50"/>
     </row>
@@ -2614,7 +3198,7 @@
       <c r="D51" s="8"/>
       <c r="E51" s="8"/>
       <c r="F51" s="9"/>
-      <c r="G51" s="6"/>
+      <c r="G51" s="62"/>
       <c r="H51" s="9"/>
       <c r="I51"/>
     </row>
@@ -2625,54 +3209,27 @@
       <c r="D52" s="8"/>
       <c r="E52" s="8"/>
       <c r="F52" s="9"/>
-      <c r="G52" s="6"/>
+      <c r="G52" s="62"/>
       <c r="H52" s="9"/>
       <c r="I52"/>
     </row>
-    <row r="53" spans="1:9">
-      <c r="A53" s="6"/>
-      <c r="B53" s="8"/>
-      <c r="C53" s="7"/>
-      <c r="D53" s="8"/>
-      <c r="E53" s="8"/>
-      <c r="F53" s="9"/>
-      <c r="G53" s="6"/>
-      <c r="H53" s="9"/>
-      <c r="I53"/>
-    </row>
-    <row r="54" spans="1:9">
-      <c r="A54" s="6"/>
-      <c r="B54" s="8"/>
-      <c r="C54" s="7"/>
-      <c r="D54" s="8"/>
-      <c r="E54" s="8"/>
-      <c r="F54" s="9"/>
-      <c r="G54" s="6"/>
-      <c r="H54" s="9"/>
-      <c r="I54"/>
-    </row>
-    <row r="55" spans="1:9">
-      <c r="A55" s="6"/>
-      <c r="B55" s="8"/>
-      <c r="C55" s="7"/>
-      <c r="D55" s="8"/>
-      <c r="E55" s="8"/>
-      <c r="F55" s="9"/>
-      <c r="G55" s="6"/>
-      <c r="H55" s="9"/>
-      <c r="I55"/>
-    </row>
   </sheetData>
   <conditionalFormatting sqref="B1:C1">
-    <cfRule type="notContainsBlanks" priority="2">
+    <cfRule type="notContainsBlanks" priority="5">
       <formula>LEN(TRIM(B1))&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="E2">
+    <cfRule type="duplicateValues" dxfId="1" priority="3"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E3">
+    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
+  </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2:A33" xr:uid="{4D257AA8-3FDB-42B7-A450-B3788B0ABB12}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2:A30" xr:uid="{4D257AA8-3FDB-42B7-A450-B3788B0ABB12}">
       <formula1>$J$2</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G41" xr:uid="{5FAA0C61-6912-46B8-8149-B719594B77CB}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G38" xr:uid="{5FAA0C61-6912-46B8-8149-B719594B77CB}">
       <formula1>"Vistoria Frustrada;,Vistoria Recusada,Bônus;,Desistência;,Inadimplência;,Política de Aceitação;,Duplicidade;,Demais Motivos,Falta de Vistoria;,"</formula1>
     </dataValidation>
   </dataValidations>
@@ -2720,7 +3277,7 @@
       <c r="H1" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="33" t="s">
+      <c r="I1" s="32" t="s">
         <v>8</v>
       </c>
     </row>
@@ -3883,7 +4440,7 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="44" t="s">
+      <c r="H1" s="43" t="s">
         <v>7</v>
       </c>
       <c r="I1" s="5" t="s">
@@ -3896,11 +4453,11 @@
       </c>
       <c r="B2" s="7"/>
       <c r="C2" s="28"/>
-      <c r="D2" s="47"/>
+      <c r="D2" s="46"/>
       <c r="E2" s="18"/>
       <c r="F2" s="19"/>
-      <c r="G2" s="42"/>
-      <c r="H2" s="39"/>
+      <c r="G2" s="41"/>
+      <c r="H2" s="38"/>
       <c r="I2" s="27"/>
     </row>
     <row r="3" spans="1:9">
@@ -3912,8 +4469,8 @@
       <c r="D3" s="25"/>
       <c r="E3" s="18"/>
       <c r="F3" s="19"/>
-      <c r="G3" s="42"/>
-      <c r="H3" s="39"/>
+      <c r="G3" s="41"/>
+      <c r="H3" s="38"/>
       <c r="I3" s="27"/>
     </row>
     <row r="4" spans="1:9">
@@ -3925,8 +4482,8 @@
       <c r="D4" s="25"/>
       <c r="E4" s="18"/>
       <c r="F4" s="19"/>
-      <c r="G4" s="42"/>
-      <c r="H4" s="39"/>
+      <c r="G4" s="41"/>
+      <c r="H4" s="38"/>
       <c r="I4" s="27"/>
     </row>
     <row r="5" spans="1:9">
@@ -3938,8 +4495,8 @@
       <c r="D5" s="25"/>
       <c r="E5" s="18"/>
       <c r="F5" s="19"/>
-      <c r="G5" s="42"/>
-      <c r="H5" s="40"/>
+      <c r="G5" s="41"/>
+      <c r="H5" s="39"/>
       <c r="I5" s="27"/>
     </row>
     <row r="6" spans="1:9">
@@ -3951,8 +4508,8 @@
       <c r="D6" s="25"/>
       <c r="E6" s="18"/>
       <c r="F6" s="19"/>
-      <c r="G6" s="43"/>
-      <c r="H6" s="41"/>
+      <c r="G6" s="42"/>
+      <c r="H6" s="40"/>
       <c r="I6" s="27"/>
     </row>
     <row r="7" spans="1:9">
@@ -3964,8 +4521,8 @@
       <c r="D7" s="25"/>
       <c r="E7" s="18"/>
       <c r="F7" s="19"/>
-      <c r="G7" s="45"/>
-      <c r="H7" s="41"/>
+      <c r="G7" s="44"/>
+      <c r="H7" s="40"/>
       <c r="I7" s="27"/>
     </row>
     <row r="8" spans="1:9">
@@ -3977,8 +4534,8 @@
       <c r="D8" s="25"/>
       <c r="E8" s="18"/>
       <c r="F8" s="19"/>
-      <c r="G8" s="46"/>
-      <c r="H8" s="41"/>
+      <c r="G8" s="45"/>
+      <c r="H8" s="40"/>
       <c r="I8" s="27"/>
     </row>
     <row r="9" spans="1:9">
@@ -3990,8 +4547,8 @@
       <c r="D9" s="25"/>
       <c r="E9" s="18"/>
       <c r="F9" s="19"/>
-      <c r="G9" s="46"/>
-      <c r="H9" s="39"/>
+      <c r="G9" s="45"/>
+      <c r="H9" s="38"/>
       <c r="I9" s="27"/>
     </row>
     <row r="10" spans="1:9">
@@ -4003,8 +4560,8 @@
       <c r="D10" s="25"/>
       <c r="E10" s="18"/>
       <c r="F10" s="19"/>
-      <c r="G10" s="46"/>
-      <c r="H10" s="39"/>
+      <c r="G10" s="45"/>
+      <c r="H10" s="38"/>
       <c r="I10" s="27"/>
     </row>
     <row r="11" spans="1:9">
@@ -4016,8 +4573,8 @@
       <c r="D11" s="25"/>
       <c r="E11" s="18"/>
       <c r="F11" s="19"/>
-      <c r="G11" s="46"/>
-      <c r="H11" s="39"/>
+      <c r="G11" s="45"/>
+      <c r="H11" s="38"/>
       <c r="I11" s="27"/>
     </row>
     <row r="12" spans="1:9">
@@ -4029,8 +4586,8 @@
       <c r="D12" s="25"/>
       <c r="E12" s="18"/>
       <c r="F12" s="19"/>
-      <c r="G12" s="46"/>
-      <c r="H12" s="39"/>
+      <c r="G12" s="45"/>
+      <c r="H12" s="38"/>
       <c r="I12" s="27"/>
     </row>
     <row r="13" spans="1:9">
@@ -4042,8 +4599,8 @@
       <c r="D13" s="25"/>
       <c r="E13" s="18"/>
       <c r="F13" s="19"/>
-      <c r="G13" s="46"/>
-      <c r="H13" s="39"/>
+      <c r="G13" s="45"/>
+      <c r="H13" s="38"/>
       <c r="I13" s="27"/>
     </row>
     <row r="14" spans="1:9">
@@ -4055,8 +4612,8 @@
       <c r="D14" s="25"/>
       <c r="E14" s="18"/>
       <c r="F14" s="19"/>
-      <c r="G14" s="46"/>
-      <c r="H14" s="39"/>
+      <c r="G14" s="45"/>
+      <c r="H14" s="38"/>
       <c r="I14" s="27"/>
     </row>
     <row r="15" spans="1:9">
@@ -4068,8 +4625,8 @@
       <c r="D15" s="25"/>
       <c r="E15" s="18"/>
       <c r="F15" s="19"/>
-      <c r="G15" s="46"/>
-      <c r="H15" s="39"/>
+      <c r="G15" s="45"/>
+      <c r="H15" s="38"/>
       <c r="I15" s="27"/>
     </row>
     <row r="16" spans="1:9">
@@ -4081,8 +4638,8 @@
       <c r="D16" s="25"/>
       <c r="E16" s="18"/>
       <c r="F16" s="12"/>
-      <c r="G16" s="46"/>
-      <c r="H16" s="39"/>
+      <c r="G16" s="45"/>
+      <c r="H16" s="38"/>
       <c r="I16" s="27"/>
     </row>
     <row r="17" spans="1:9" ht="15" customHeight="1">
@@ -4094,8 +4651,8 @@
       <c r="D17" s="25"/>
       <c r="E17" s="18"/>
       <c r="F17" s="12"/>
-      <c r="G17" s="42"/>
-      <c r="H17" s="39"/>
+      <c r="G17" s="41"/>
+      <c r="H17" s="38"/>
       <c r="I17" s="27"/>
     </row>
     <row r="18" spans="1:9">
@@ -4107,8 +4664,8 @@
       <c r="D18" s="25"/>
       <c r="E18" s="18"/>
       <c r="F18" s="12"/>
-      <c r="G18" s="46"/>
-      <c r="H18" s="39"/>
+      <c r="G18" s="45"/>
+      <c r="H18" s="38"/>
       <c r="I18" s="27"/>
     </row>
     <row r="19" spans="1:9">
@@ -4116,9 +4673,9 @@
       <c r="B19" s="8"/>
       <c r="C19" s="7"/>
       <c r="D19" s="23"/>
-      <c r="E19" s="35"/>
-      <c r="F19" s="37"/>
-      <c r="G19" s="34"/>
+      <c r="E19" s="34"/>
+      <c r="F19" s="36"/>
+      <c r="G19" s="33"/>
       <c r="H19" s="9"/>
       <c r="I19" s="27"/>
     </row>
@@ -4129,7 +4686,7 @@
       <c r="D20" s="8"/>
       <c r="E20" s="8"/>
       <c r="F20" s="15"/>
-      <c r="G20" s="34"/>
+      <c r="G20" s="33"/>
       <c r="H20" s="9"/>
       <c r="I20" s="27"/>
     </row>
@@ -4140,7 +4697,7 @@
       <c r="D21" s="8"/>
       <c r="E21" s="8"/>
       <c r="F21" s="9"/>
-      <c r="G21" s="34"/>
+      <c r="G21" s="33"/>
       <c r="H21" s="9"/>
       <c r="I21" s="27"/>
     </row>
@@ -4151,7 +4708,7 @@
       <c r="D22" s="8"/>
       <c r="E22" s="8"/>
       <c r="F22" s="9"/>
-      <c r="G22" s="34"/>
+      <c r="G22" s="33"/>
       <c r="H22" s="9"/>
       <c r="I22" s="27"/>
     </row>
@@ -4162,7 +4719,7 @@
       <c r="D23" s="8"/>
       <c r="E23" s="8"/>
       <c r="F23" s="9"/>
-      <c r="G23" s="34"/>
+      <c r="G23" s="33"/>
       <c r="H23" s="9"/>
       <c r="I23" s="27"/>
     </row>
@@ -4173,7 +4730,7 @@
       <c r="D24" s="8"/>
       <c r="E24" s="8"/>
       <c r="F24" s="9"/>
-      <c r="G24" s="34"/>
+      <c r="G24" s="33"/>
       <c r="H24" s="9"/>
       <c r="I24" s="27"/>
     </row>
@@ -4604,7 +5161,7 @@
       <c r="F3" s="12"/>
       <c r="G3" s="20"/>
       <c r="H3" s="9"/>
-      <c r="I3" s="38"/>
+      <c r="I3" s="37"/>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="6" t="s">
@@ -4637,8 +5194,8 @@
       <c r="B6" s="7"/>
       <c r="C6" s="7"/>
       <c r="D6" s="23"/>
-      <c r="E6" s="35"/>
-      <c r="F6" s="36"/>
+      <c r="E6" s="34"/>
+      <c r="F6" s="35"/>
       <c r="G6" s="6"/>
       <c r="H6" s="9"/>
       <c r="I6" s="27"/>
@@ -5795,8 +6352,60 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010006E7B04763359F4AAB0FC84D5027BFC8" ma:contentTypeVersion="43" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="abf1b9912853fe4a934dbc2373304754">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xmlns:ns3="ea6c6725-5210-4d6a-93cc-4cf85111ac5e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="d8d96f03b10d24171ef462918d18284e" ns1:_="" ns2:_="" ns3:_="">
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_dlc_DocId xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">QAFFA7D2F2TC-2102087286-494890</_dlc_DocId>
+    <_dlc_DocIdUrl xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">
+      <Url>https://allianzms.sharepoint.com/teams/BR0010-4356589/_layouts/15/DocIdRedir.aspx?ID=QAFFA7D2F2TC-2102087286-494890</Url>
+      <Description>QAFFA7D2F2TC-2102087286-494890</Description>
+    </_dlc_DocIdUrl>
+    <DossierOwner xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </DossierOwner>
+    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <ccca9d190a3c43e89f73773ee806c8b5 xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </ccca9d190a3c43e89f73773ee806c8b5>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="ea6c6725-5210-4d6a-93cc-4cf85111ac5e">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <ContractDate xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
+    <MailPreviewData xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
+    <_Flow_SignoffStatus xmlns="ea6c6725-5210-4d6a-93cc-4cf85111ac5e" xsi:nil="true"/>
+    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <ContractExpirationDate xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
+    <DossierStatus xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
+    <ia4b831ccad64069ad2e0cbd870e9b8a xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </ia4b831ccad64069ad2e0cbd870e9b8a>
+    <TaxCatchAll xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
+    <alteradopor xmlns="ea6c6725-5210-4d6a-93cc-4cf85111ac5e">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </alteradopor>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x01010006E7B04763359F4AAB0FC84D5027BFC8" ma:contentTypeVersion="43" ma:contentTypeDescription="Criar um novo documento." ma:contentTypeScope="" ma:versionID="32fbec5585ae01a22f32af5838af0c4d">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xmlns:ns3="ea6c6725-5210-4d6a-93cc-4cf85111ac5e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="7b2552458edfdc024ce707f91c2c891f" ns1:_="" ns2:_="" ns3:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
     <xsd:import namespace="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea"/>
     <xsd:import namespace="ea6c6725-5210-4d6a-93cc-4cf85111ac5e"/>
@@ -5844,12 +6453,12 @@
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="http://schemas.microsoft.com/sharepoint/v3" elementFormDefault="qualified">
     <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
     <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="_ip_UnifiedCompliancePolicyProperties" ma:index="23" nillable="true" ma:displayName="Unified Compliance Policy Properties" ma:hidden="true" ma:internalName="_ip_UnifiedCompliancePolicyProperties">
+    <xsd:element name="_ip_UnifiedCompliancePolicyProperties" ma:index="23" nillable="true" ma:displayName="Propriedades da Política de Conformidade Unificada" ma:hidden="true" ma:internalName="_ip_UnifiedCompliancePolicyProperties">
       <xsd:simpleType>
         <xsd:restriction base="dms:Note"/>
       </xsd:simpleType>
     </xsd:element>
-    <xsd:element name="_ip_UnifiedCompliancePolicyUIAction" ma:index="24" nillable="true" ma:displayName="Unified Compliance Policy UI Action" ma:hidden="true" ma:internalName="_ip_UnifiedCompliancePolicyUIAction">
+    <xsd:element name="_ip_UnifiedCompliancePolicyUIAction" ma:index="24" nillable="true" ma:displayName="Ação de IU da Política de Conformidade Unificada" ma:hidden="true" ma:internalName="_ip_UnifiedCompliancePolicyUIAction">
       <xsd:simpleType>
         <xsd:restriction base="dms:Text"/>
       </xsd:simpleType>
@@ -5858,12 +6467,12 @@
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" elementFormDefault="qualified">
     <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
     <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="_dlc_DocId" ma:index="8" nillable="true" ma:displayName="Document ID Value" ma:description="The value of the document ID assigned to this item." ma:indexed="true" ma:internalName="_dlc_DocId" ma:readOnly="true">
+    <xsd:element name="_dlc_DocId" ma:index="8" nillable="true" ma:displayName="Valor do ID do Documento" ma:description="O valor do ID do documento atribuído a este item." ma:indexed="true" ma:internalName="_dlc_DocId" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Text"/>
       </xsd:simpleType>
     </xsd:element>
-    <xsd:element name="_dlc_DocIdUrl" ma:index="9" nillable="true" ma:displayName="Document ID" ma:description="Permanent link to this document." ma:hidden="true" ma:internalName="_dlc_DocIdUrl" ma:readOnly="true">
+    <xsd:element name="_dlc_DocIdUrl" ma:index="9" nillable="true" ma:displayName="ID do Documento" ma:description="Ligação permanente a este documento." ma:hidden="true" ma:internalName="_dlc_DocIdUrl" ma:readOnly="true">
       <xsd:complexType>
         <xsd:complexContent>
           <xsd:extension base="dms:URL">
@@ -5946,7 +6555,7 @@
         <xsd:restriction base="dms:DateTime"/>
       </xsd:simpleType>
     </xsd:element>
-    <xsd:element name="SharedWithUsers" ma:index="19" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
+    <xsd:element name="SharedWithUsers" ma:index="19" nillable="true" ma:displayName="Partilhado Com" ma:internalName="SharedWithUsers" ma:readOnly="true">
       <xsd:complexType>
         <xsd:complexContent>
           <xsd:extension base="dms:UserMulti">
@@ -5965,7 +6574,7 @@
         </xsd:complexContent>
       </xsd:complexType>
     </xsd:element>
-    <xsd:element name="SharedWithDetails" ma:index="20" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
+    <xsd:element name="SharedWithDetails" ma:index="20" nillable="true" ma:displayName="Detalhes de Partilhado Com" ma:internalName="SharedWithDetails" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Note">
           <xsd:maxLength value="255"/>
@@ -5998,7 +6607,7 @@
         <xsd:restriction base="dms:Note"/>
       </xsd:simpleType>
     </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="26" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="10820af1-e82f-496e-bbcb-d9502914b7b2" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="26" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Etiquetas de Imagem" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="10820af1-e82f-496e-bbcb-d9502914b7b2" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
       <xsd:complexType>
         <xsd:sequence>
           <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
@@ -6076,8 +6685,8 @@
         <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
         <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
         <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Tipo de Conteúdo"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Título"/>
         <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
         <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
         <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
@@ -6166,58 +6775,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_dlc_DocId xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">QAFFA7D2F2TC-2102087286-494890</_dlc_DocId>
-    <_dlc_DocIdUrl xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">
-      <Url>https://allianzms.sharepoint.com/teams/BR0010-4356589/_layouts/15/DocIdRedir.aspx?ID=QAFFA7D2F2TC-2102087286-494890</Url>
-      <Description>QAFFA7D2F2TC-2102087286-494890</Description>
-    </_dlc_DocIdUrl>
-    <DossierOwner xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </DossierOwner>
-    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <ccca9d190a3c43e89f73773ee806c8b5 xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </ccca9d190a3c43e89f73773ee806c8b5>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="ea6c6725-5210-4d6a-93cc-4cf85111ac5e">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <ContractDate xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
-    <MailPreviewData xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
-    <_Flow_SignoffStatus xmlns="ea6c6725-5210-4d6a-93cc-4cf85111ac5e" xsi:nil="true"/>
-    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <ContractExpirationDate xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
-    <DossierStatus xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
-    <ia4b831ccad64069ad2e0cbd870e9b8a xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </ia4b831ccad64069ad2e0cbd870e9b8a>
-    <TaxCatchAll xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
-    <alteradopor xmlns="ea6c6725-5210-4d6a-93cc-4cf85111ac5e">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </alteradopor>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <spe:Receivers xmlns:spe="http://schemas.microsoft.com/sharepoint/events">
@@ -6269,7 +6826,7 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{52D5A726-16FA-4932-8BF5-855F9B379AB9}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BC9CB02D-0F63-4CE2-B316-61A87327416C}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -6277,7 +6834,7 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BC9CB02D-0F63-4CE2-B316-61A87327416C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{11932F8B-2F43-467F-BFC3-DB084CEB998D}"/>
 </file>
 
 <file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>

--- a/Data Files/Backoffce/IndexacaoFG/Arquivos/Relatório de Recusas  04.08.2025 a 10.08.2025.xlsx
+++ b/Data Files/Backoffce/IndexacaoFG/Arquivos/Relatório de Recusas  04.08.2025 a 10.08.2025.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://allianzms.sharepoint.com/teams/BR0010-4356589/Shared Documents/BACK-OFFICE SME/Santander/2025/Relatório de Recusas/05. Maio/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2035410F-39B7-4362-9EAA-0009B0D0A2DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{F8A06A45-B4BB-4E96-ACB0-5E0421BF1705}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="19530" windowHeight="9780" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="19530" windowHeight="9780" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="04.08" sheetId="2" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="330" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="248" uniqueCount="51">
   <si>
     <t>SEGURADORA</t>
   </si>
@@ -196,117 +196,12 @@
   <si>
     <t xml:space="preserve">GLAYCE APARECIDA ESPINULA                    </t>
   </si>
-  <si>
-    <t>22 876 062 REGINALDO DA COSTA ME CNPJ 22876062000102</t>
-  </si>
-  <si>
-    <t>Chassi Irregular</t>
-  </si>
-  <si>
-    <t>R PANTOJA RODRIGUES LTDA ME CNPJ 38066386000107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">JOSE ERNANDES PEREIRA DA SILVA               </t>
-  </si>
-  <si>
-    <t>Bônus;</t>
-  </si>
-  <si>
-    <t>Conforme CBE pela regra de mudança de cobertur
-a, da 2 para 1, ocorre a redução de 1 classe de bônus, assim sendo
-o correto bônus 0.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MARCIO FERNANDO RIBEIRO DA SILVA             </t>
-  </si>
-  <si>
-    <t>NUP Cancelamento 04.08.2025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FELIPE DIEGO DE ARRUDA                       </t>
-  </si>
-  <si>
-    <t xml:space="preserve">SILVIA APARECIDA DE OLIVEIRA                 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">JULIO CESAR BUGMANN                          </t>
-  </si>
-  <si>
-    <t xml:space="preserve">E S ROCHA EPP                                </t>
-  </si>
-  <si>
-    <t xml:space="preserve">FELIPE SANTOS DUTRA                          </t>
-  </si>
-  <si>
-    <t xml:space="preserve">TOMAS BARBIERI                               </t>
-  </si>
-  <si>
-    <t xml:space="preserve">GISELY FRANCE ABRANTES                       </t>
-  </si>
-  <si>
-    <t>Para que possamos prosseguir
-coma liberação do bloqueio será necessário a apresentação do en
-dosso de cancelamento emitido</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KARINA CARLA DE ARAUJO COSTA                 </t>
-  </si>
-  <si>
-    <t>31 867 065 MARIA APARECIDA PINTO DE ARAUJO ME</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FRANCIELMA DE MESQUITA SOUSA MENDES          </t>
-  </si>
-  <si>
-    <t xml:space="preserve">ROBERTO PONTES FERNANDES                     </t>
-  </si>
-  <si>
-    <t xml:space="preserve">THIAGO SABINO DE SOUZA                       </t>
-  </si>
-  <si>
-    <t xml:space="preserve">AMANDA MOLINA GARCIA DOS SANTOS              </t>
-  </si>
-  <si>
-    <t xml:space="preserve">CLAUDIA MARIA NASSIF ARRUDA DAVID            </t>
-  </si>
-  <si>
-    <t>Duplicidade;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">	Santander - Veículo em duplicidade com proposta </t>
-  </si>
-  <si>
-    <t xml:space="preserve">MARIANGELA DE PAULA JUDICE                   </t>
-  </si>
-  <si>
-    <t>apólice anterior consta classe de
-bônus3, não havendo sinistro, conforme regra concede 1 classe de b
-ônus, assim sendo o correto bônus 4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">JOAO DONIZETI CHIUZULI                       </t>
-  </si>
-  <si>
-    <t>***FRUSTRADO**CLIENTE NÃO CORRIGIU AS FOTOS INCORRETAS - PRAZO EXPIRADO FOTO INCORRETA: Foto 45º - Frente e Lateral Esquerda (Foto com placa obstruída, Foto com baixa iluminação). Foto 45º - Traseira e Lateral Direita (Foto com baixa iluminação).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ANDREZA FERNANDES DOS PASSOS DE PAULA        </t>
-  </si>
-  <si>
-    <t xml:space="preserve">VICTOR FERRER BORTONI                        </t>
-  </si>
-  <si>
-    <t xml:space="preserve">INOVA STEEL ESTRUTURAS METALICAS LTDA ME     </t>
-  </si>
-  <si>
-    <t xml:space="preserve">4TECH AUTOMACAO LTDA EPP                     </t>
-  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -350,13 +245,6 @@
       <family val="2"/>
       <charset val="1"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -372,7 +260,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="17">
+  <borders count="15">
     <border>
       <left/>
       <right/>
@@ -558,38 +446,12 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color theme="4" tint="0.39997558519241921"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="65">
+  <cellXfs count="54">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -667,6 +529,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -718,64 +581,13 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal_Plan2_1" xfId="1" xr:uid="{69F13A52-20D9-46CA-8619-BC7A1BA09FD8}"/>
   </cellStyles>
-  <dxfs count="2">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-  </dxfs>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleMedium9"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -1244,7 +1056,7 @@
       <c r="E5" s="21">
         <v>3450043179</v>
       </c>
-      <c r="F5" s="49" t="s">
+      <c r="F5" s="50" t="s">
         <v>19</v>
       </c>
       <c r="G5" s="20" t="s">
@@ -1268,7 +1080,7 @@
       <c r="D6" s="25">
         <v>133632327</v>
       </c>
-      <c r="E6" s="47">
+      <c r="E6" s="48">
         <v>3450038405</v>
       </c>
       <c r="F6" s="12" t="s">
@@ -1297,7 +1109,7 @@
       <c r="D7" s="25">
         <v>133624469</v>
       </c>
-      <c r="E7" s="47">
+      <c r="E7" s="48">
         <v>3450037811</v>
       </c>
       <c r="F7" s="12" t="s">
@@ -1326,7 +1138,7 @@
       <c r="D8" s="25">
         <v>133625917</v>
       </c>
-      <c r="E8" s="47">
+      <c r="E8" s="48">
         <v>3450037910</v>
       </c>
       <c r="F8" s="12" t="s">
@@ -1355,7 +1167,7 @@
       <c r="D9" s="25">
         <v>133613919</v>
       </c>
-      <c r="E9" s="47">
+      <c r="E9" s="48">
         <v>3450037470</v>
       </c>
       <c r="F9" s="12" t="s">
@@ -1384,7 +1196,7 @@
       <c r="D10" s="25">
         <v>133630273</v>
       </c>
-      <c r="E10" s="47">
+      <c r="E10" s="48">
         <v>3450038207</v>
       </c>
       <c r="F10" s="12" t="s">
@@ -1413,7 +1225,7 @@
       <c r="D11" s="25">
         <v>133635781</v>
       </c>
-      <c r="E11" s="47">
+      <c r="E11" s="48">
         <v>3450038515</v>
       </c>
       <c r="F11" s="12" t="s">
@@ -1442,7 +1254,7 @@
       <c r="D12" s="25">
         <v>133664790</v>
       </c>
-      <c r="E12" s="47">
+      <c r="E12" s="48">
         <v>3450039736</v>
       </c>
       <c r="F12" s="12" t="s">
@@ -1471,7 +1283,7 @@
       <c r="D13" s="25">
         <v>133673295</v>
       </c>
-      <c r="E13" s="47">
+      <c r="E13" s="48">
         <v>3450040253</v>
       </c>
       <c r="F13" s="12" t="s">
@@ -1500,7 +1312,7 @@
       <c r="D14" s="25">
         <v>133659080</v>
       </c>
-      <c r="E14" s="47">
+      <c r="E14" s="48">
         <v>3450039241</v>
       </c>
       <c r="F14" s="12" t="s">
@@ -1529,7 +1341,7 @@
       <c r="D15" s="25">
         <v>133729067</v>
       </c>
-      <c r="E15" s="47">
+      <c r="E15" s="48">
         <v>3450042970</v>
       </c>
       <c r="F15" s="12" t="s">
@@ -1558,7 +1370,7 @@
       <c r="D16" s="25">
         <v>133649747</v>
       </c>
-      <c r="E16" s="47">
+      <c r="E16" s="48">
         <v>3450038966</v>
       </c>
       <c r="F16" s="12" t="s">
@@ -1587,7 +1399,7 @@
       <c r="D17" s="25">
         <v>133757334</v>
       </c>
-      <c r="E17" s="47">
+      <c r="E17" s="48">
         <v>3450044510</v>
       </c>
       <c r="F17" s="12" t="s">
@@ -1596,7 +1408,7 @@
       <c r="G17" s="20" t="s">
         <v>38</v>
       </c>
-      <c r="H17" s="9" t="s">
+      <c r="H17" s="53" t="s">
         <v>39</v>
       </c>
       <c r="I17" s="27">
@@ -1616,7 +1428,7 @@
       <c r="D18" s="25">
         <v>133613216</v>
       </c>
-      <c r="E18" s="47">
+      <c r="E18" s="48">
         <v>3450037437</v>
       </c>
       <c r="F18" s="12" t="s">
@@ -1645,7 +1457,7 @@
       <c r="D19" s="25">
         <v>133615484</v>
       </c>
-      <c r="E19" s="47">
+      <c r="E19" s="48">
         <v>3450037514</v>
       </c>
       <c r="F19" s="12" t="s">
@@ -1674,7 +1486,7 @@
       <c r="D20" s="25">
         <v>133627426</v>
       </c>
-      <c r="E20" s="47">
+      <c r="E20" s="48">
         <v>3450037976</v>
       </c>
       <c r="F20" s="12" t="s">
@@ -1703,7 +1515,7 @@
       <c r="D21" s="25">
         <v>133628230</v>
       </c>
-      <c r="E21" s="47">
+      <c r="E21" s="48">
         <v>3450038053</v>
       </c>
       <c r="F21" s="12" t="s">
@@ -1732,7 +1544,7 @@
       <c r="D22" s="25">
         <v>133629632</v>
       </c>
-      <c r="E22" s="47">
+      <c r="E22" s="48">
         <v>3450038141</v>
       </c>
       <c r="F22" s="12" t="s">
@@ -1761,7 +1573,7 @@
       <c r="D23" s="25">
         <v>133630563</v>
       </c>
-      <c r="E23" s="47">
+      <c r="E23" s="48">
         <v>3450038240</v>
       </c>
       <c r="F23" s="12" t="s">
@@ -1790,7 +1602,7 @@
       <c r="D24" s="25">
         <v>133630656</v>
       </c>
-      <c r="E24" s="47">
+      <c r="E24" s="48">
         <v>3450038273</v>
       </c>
       <c r="F24" s="12" t="s">
@@ -1819,7 +1631,7 @@
       <c r="D25" s="25">
         <v>133631738</v>
       </c>
-      <c r="E25" s="47">
+      <c r="E25" s="48">
         <v>3450038340</v>
       </c>
       <c r="F25" s="12" t="s">
@@ -1840,8 +1652,8 @@
       <c r="B26" s="7"/>
       <c r="C26" s="28"/>
       <c r="D26" s="25"/>
-      <c r="E26" s="48"/>
-      <c r="F26" s="50"/>
+      <c r="E26" s="49"/>
+      <c r="F26" s="51"/>
       <c r="G26" s="20"/>
       <c r="H26" s="9"/>
       <c r="I26" s="27"/>
@@ -1851,7 +1663,7 @@
       <c r="B27" s="7"/>
       <c r="C27" s="28"/>
       <c r="D27" s="25"/>
-      <c r="E27" s="48"/>
+      <c r="E27" s="49"/>
       <c r="F27" s="19"/>
       <c r="G27" s="20"/>
       <c r="H27" s="9"/>
@@ -1861,7 +1673,7 @@
       <c r="A28" s="6"/>
       <c r="B28" s="7"/>
       <c r="C28" s="7"/>
-      <c r="D28" s="51"/>
+      <c r="D28" s="52"/>
       <c r="E28" s="18"/>
       <c r="F28" s="19"/>
       <c r="G28" s="20"/>
@@ -2181,7 +1993,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FFA17127-7620-4DD9-9061-6C654E2EC5C2}">
-  <dimension ref="A1:I52"/>
+  <dimension ref="A1:I55"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
@@ -2190,7 +2002,7 @@
     <col min="4" max="4" width="27.7109375" style="17" customWidth="1"/>
     <col min="5" max="5" width="18.5703125" customWidth="1"/>
     <col min="6" max="6" width="31.5703125" customWidth="1"/>
-    <col min="7" max="7" width="19.7109375" style="63" customWidth="1"/>
+    <col min="7" max="7" width="19.7109375" customWidth="1"/>
     <col min="8" max="8" width="24" customWidth="1"/>
     <col min="9" max="9" width="22.7109375" style="16" customWidth="1"/>
   </cols>
@@ -2228,703 +2040,307 @@
       <c r="A2" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="7">
-        <v>45870</v>
-      </c>
-      <c r="C2" s="28">
-        <v>45874</v>
-      </c>
-      <c r="D2" s="25" t="s">
-        <v>11</v>
-      </c>
-      <c r="E2" s="58">
-        <v>3450042651</v>
-      </c>
-      <c r="F2" s="12" t="s">
-        <v>51</v>
-      </c>
-      <c r="G2" s="60" t="s">
-        <v>16</v>
-      </c>
-      <c r="H2" s="12" t="s">
-        <v>52</v>
-      </c>
+      <c r="B2" s="7"/>
+      <c r="C2" s="28"/>
+      <c r="D2" s="25"/>
+      <c r="E2" s="18"/>
+      <c r="F2" s="12"/>
+      <c r="G2" s="20"/>
+      <c r="H2" s="12"/>
       <c r="I2" s="27"/>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="7">
-        <v>45873</v>
-      </c>
-      <c r="C3" s="28">
-        <v>45874</v>
-      </c>
-      <c r="D3" s="57" t="s">
-        <v>11</v>
-      </c>
-      <c r="E3" s="58">
-        <v>3450044037</v>
-      </c>
-      <c r="F3" s="12" t="s">
-        <v>53</v>
-      </c>
-      <c r="G3" s="60" t="s">
-        <v>16</v>
-      </c>
-      <c r="H3" s="12" t="s">
-        <v>52</v>
-      </c>
+      <c r="B3" s="7"/>
+      <c r="C3" s="28"/>
+      <c r="D3" s="25"/>
+      <c r="E3" s="18"/>
+      <c r="F3" s="12"/>
+      <c r="G3" s="20"/>
+      <c r="H3" s="9"/>
       <c r="I3" s="27"/>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="7">
-        <v>45868</v>
-      </c>
-      <c r="C4" s="28">
-        <v>45874</v>
-      </c>
-      <c r="D4" s="55">
-        <v>133569706</v>
-      </c>
-      <c r="E4" s="56">
-        <v>3450035633</v>
-      </c>
-      <c r="F4" s="52" t="s">
-        <v>54</v>
-      </c>
-      <c r="G4" s="60" t="s">
-        <v>55</v>
-      </c>
-      <c r="H4" s="59" t="s">
-        <v>56</v>
-      </c>
-      <c r="I4" s="27">
-        <v>45866</v>
-      </c>
+      <c r="B4" s="7"/>
+      <c r="C4" s="28"/>
+      <c r="D4" s="25"/>
+      <c r="E4" s="18"/>
+      <c r="F4" s="12"/>
+      <c r="G4" s="20"/>
+      <c r="H4" s="9"/>
+      <c r="I4" s="27"/>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="7">
-        <v>45872</v>
-      </c>
-      <c r="C5" s="28">
-        <v>45874</v>
-      </c>
-      <c r="D5" s="55">
-        <v>133653803</v>
-      </c>
-      <c r="E5" s="48">
-        <v>3450039164</v>
-      </c>
-      <c r="F5" s="53" t="s">
-        <v>57</v>
-      </c>
-      <c r="G5" s="60" t="s">
-        <v>13</v>
-      </c>
-      <c r="H5" s="59" t="s">
-        <v>58</v>
-      </c>
-      <c r="I5" s="27">
-        <v>45873</v>
-      </c>
+      <c r="B5" s="7"/>
+      <c r="C5" s="28"/>
+      <c r="D5" s="25"/>
+      <c r="E5" s="18"/>
+      <c r="F5" s="12"/>
+      <c r="G5" s="20"/>
+      <c r="H5" s="9"/>
+      <c r="I5" s="27"/>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="7">
-        <v>45863</v>
-      </c>
-      <c r="C6" s="28">
-        <v>45874</v>
-      </c>
-      <c r="D6" s="55">
-        <v>133639832</v>
-      </c>
-      <c r="E6" s="48">
-        <v>3450038438</v>
-      </c>
-      <c r="F6" s="53" t="s">
-        <v>59</v>
-      </c>
-      <c r="G6" s="60" t="s">
-        <v>21</v>
-      </c>
-      <c r="H6" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="I6" s="27">
-        <v>45863</v>
-      </c>
+      <c r="B6" s="7"/>
+      <c r="C6" s="28"/>
+      <c r="D6" s="25"/>
+      <c r="E6" s="18"/>
+      <c r="F6" s="12"/>
+      <c r="G6" s="20"/>
+      <c r="H6" s="22"/>
+      <c r="I6" s="27"/>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B7" s="7">
-        <v>45860</v>
-      </c>
-      <c r="C7" s="28">
-        <v>45874</v>
-      </c>
-      <c r="D7" s="55">
-        <v>133636937</v>
-      </c>
-      <c r="E7" s="48">
-        <v>3450034885</v>
-      </c>
-      <c r="F7" s="53" t="s">
-        <v>60</v>
-      </c>
-      <c r="G7" s="61" t="s">
-        <v>21</v>
-      </c>
-      <c r="H7" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="I7" s="27">
-        <v>45860</v>
-      </c>
+      <c r="B7" s="7"/>
+      <c r="C7" s="28"/>
+      <c r="D7" s="25"/>
+      <c r="E7" s="18"/>
+      <c r="F7" s="12"/>
+      <c r="G7" s="26"/>
+      <c r="H7" s="31"/>
+      <c r="I7" s="27"/>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B8" s="7">
-        <v>45860</v>
-      </c>
-      <c r="C8" s="28">
-        <v>45874</v>
-      </c>
-      <c r="D8" s="55">
-        <v>133636970</v>
-      </c>
-      <c r="E8" s="48">
-        <v>3450034742</v>
-      </c>
-      <c r="F8" s="53" t="s">
-        <v>61</v>
-      </c>
-      <c r="G8" s="61" t="s">
-        <v>21</v>
-      </c>
-      <c r="H8" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="I8" s="27">
-        <v>45860</v>
-      </c>
+      <c r="B8" s="7"/>
+      <c r="C8" s="28"/>
+      <c r="D8" s="25"/>
+      <c r="E8" s="18"/>
+      <c r="F8" s="12"/>
+      <c r="G8" s="26"/>
+      <c r="H8" s="12"/>
+      <c r="I8" s="27"/>
     </row>
     <row r="9" spans="1:9">
       <c r="A9" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B9" s="7">
-        <v>45867</v>
-      </c>
-      <c r="C9" s="28">
-        <v>45874</v>
-      </c>
-      <c r="D9" s="55">
-        <v>133668500</v>
-      </c>
-      <c r="E9" s="48">
-        <v>3450039934</v>
-      </c>
-      <c r="F9" s="53" t="s">
-        <v>62</v>
-      </c>
-      <c r="G9" s="60" t="s">
-        <v>24</v>
-      </c>
-      <c r="H9" s="64" t="s">
-        <v>41</v>
-      </c>
-      <c r="I9" s="27">
-        <v>45867</v>
-      </c>
+      <c r="B9" s="7"/>
+      <c r="C9" s="28"/>
+      <c r="D9" s="25"/>
+      <c r="E9" s="18"/>
+      <c r="F9" s="12"/>
+      <c r="G9" s="20"/>
+      <c r="H9" s="15"/>
+      <c r="I9" s="27"/>
     </row>
     <row r="10" spans="1:9">
       <c r="A10" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B10" s="7">
-        <v>45868</v>
-      </c>
-      <c r="C10" s="28">
-        <v>45874</v>
-      </c>
-      <c r="D10" s="55">
-        <v>133692443</v>
-      </c>
-      <c r="E10" s="48">
-        <v>3450041090</v>
-      </c>
-      <c r="F10" s="53" t="s">
-        <v>63</v>
-      </c>
-      <c r="G10" s="60" t="s">
-        <v>13</v>
-      </c>
-      <c r="H10" s="59" t="s">
-        <v>58</v>
-      </c>
-      <c r="I10" s="27">
-        <v>45873</v>
-      </c>
+      <c r="B10" s="7"/>
+      <c r="C10" s="28"/>
+      <c r="D10" s="25"/>
+      <c r="E10" s="18"/>
+      <c r="F10" s="12"/>
+      <c r="G10" s="20"/>
+      <c r="H10" s="9"/>
+      <c r="I10" s="27"/>
     </row>
     <row r="11" spans="1:9">
       <c r="A11" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B11" s="7">
-        <v>45867</v>
-      </c>
-      <c r="C11" s="28">
-        <v>45874</v>
-      </c>
-      <c r="D11" s="55">
-        <v>133669604</v>
-      </c>
-      <c r="E11" s="48">
-        <v>3450040066</v>
-      </c>
-      <c r="F11" s="53" t="s">
-        <v>64</v>
-      </c>
-      <c r="G11" s="60" t="s">
-        <v>38</v>
-      </c>
-      <c r="H11" s="59" t="s">
-        <v>39</v>
-      </c>
-      <c r="I11" s="27">
-        <v>45867</v>
-      </c>
+      <c r="B11" s="7"/>
+      <c r="C11" s="28"/>
+      <c r="D11" s="25"/>
+      <c r="E11" s="18"/>
+      <c r="F11" s="12"/>
+      <c r="G11" s="20"/>
+      <c r="H11" s="9"/>
+      <c r="I11" s="27"/>
     </row>
     <row r="12" spans="1:9">
       <c r="A12" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B12" s="7">
-        <v>45891</v>
-      </c>
-      <c r="C12" s="28">
-        <v>45874</v>
-      </c>
-      <c r="D12" s="55">
-        <v>133577309</v>
-      </c>
-      <c r="E12" s="48">
-        <v>3450036007</v>
-      </c>
-      <c r="F12" s="53" t="s">
-        <v>65</v>
-      </c>
-      <c r="G12" s="60" t="s">
-        <v>55</v>
-      </c>
-      <c r="H12" s="59" t="s">
-        <v>66</v>
-      </c>
-      <c r="I12" s="27">
-        <v>45863</v>
-      </c>
+      <c r="B12" s="7"/>
+      <c r="C12" s="28"/>
+      <c r="D12" s="25"/>
+      <c r="E12" s="18"/>
+      <c r="F12" s="12"/>
+      <c r="G12" s="20"/>
+      <c r="H12" s="9"/>
+      <c r="I12" s="27"/>
     </row>
     <row r="13" spans="1:9">
       <c r="A13" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B13" s="7">
-        <v>45869</v>
-      </c>
-      <c r="C13" s="28">
-        <v>45874</v>
-      </c>
-      <c r="D13" s="55">
-        <v>133708632</v>
-      </c>
-      <c r="E13" s="48">
-        <v>3450041738</v>
-      </c>
-      <c r="F13" s="53" t="s">
-        <v>67</v>
-      </c>
-      <c r="G13" s="60" t="s">
-        <v>38</v>
-      </c>
-      <c r="H13" s="59" t="s">
-        <v>39</v>
-      </c>
-      <c r="I13" s="27">
-        <v>45869</v>
-      </c>
+      <c r="B13" s="7"/>
+      <c r="C13" s="28"/>
+      <c r="D13" s="25"/>
+      <c r="E13" s="18"/>
+      <c r="F13" s="12"/>
+      <c r="G13" s="20"/>
+      <c r="H13" s="9"/>
+      <c r="I13" s="27"/>
     </row>
     <row r="14" spans="1:9">
       <c r="A14" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B14" s="7">
-        <v>45870</v>
-      </c>
-      <c r="C14" s="28">
-        <v>45874</v>
-      </c>
-      <c r="D14" s="55">
-        <v>133723098</v>
-      </c>
-      <c r="E14" s="48">
-        <v>3450042475</v>
-      </c>
-      <c r="F14" s="53" t="s">
-        <v>68</v>
-      </c>
-      <c r="G14" s="60" t="s">
-        <v>38</v>
-      </c>
-      <c r="H14" s="59" t="s">
-        <v>39</v>
-      </c>
-      <c r="I14" s="27">
-        <v>45870</v>
-      </c>
+      <c r="B14" s="7"/>
+      <c r="C14" s="28"/>
+      <c r="D14" s="25"/>
+      <c r="E14" s="18"/>
+      <c r="F14" s="12"/>
+      <c r="G14" s="20"/>
+      <c r="H14" s="9"/>
+      <c r="I14" s="27"/>
     </row>
     <row r="15" spans="1:9">
       <c r="A15" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B15" s="7">
-        <v>45870</v>
-      </c>
-      <c r="C15" s="28">
-        <v>45874</v>
-      </c>
-      <c r="D15" s="55">
-        <v>133738294</v>
-      </c>
-      <c r="E15" s="48">
-        <v>3450043553</v>
-      </c>
-      <c r="F15" s="53" t="s">
-        <v>69</v>
-      </c>
-      <c r="G15" s="60" t="s">
-        <v>13</v>
-      </c>
-      <c r="H15" s="59" t="s">
-        <v>58</v>
-      </c>
-      <c r="I15" s="27">
-        <v>45873</v>
-      </c>
+      <c r="B15" s="7"/>
+      <c r="C15" s="28"/>
+      <c r="D15" s="25"/>
+      <c r="E15" s="18"/>
+      <c r="F15" s="12"/>
+      <c r="G15" s="20"/>
+      <c r="H15" s="9"/>
+      <c r="I15" s="27"/>
     </row>
     <row r="16" spans="1:9">
       <c r="A16" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B16" s="7">
-        <v>45899</v>
-      </c>
-      <c r="C16" s="28">
-        <v>45874</v>
-      </c>
-      <c r="D16" s="55">
-        <v>133732110</v>
-      </c>
-      <c r="E16" s="48">
-        <v>3450043135</v>
-      </c>
-      <c r="F16" s="53" t="s">
-        <v>70</v>
-      </c>
-      <c r="G16" s="60" t="s">
-        <v>13</v>
-      </c>
-      <c r="H16" s="59" t="s">
-        <v>58</v>
-      </c>
-      <c r="I16" s="27">
-        <v>45873</v>
-      </c>
+      <c r="B16" s="7"/>
+      <c r="C16" s="28"/>
+      <c r="D16" s="25"/>
+      <c r="E16" s="18"/>
+      <c r="F16" s="12"/>
+      <c r="G16" s="20"/>
+      <c r="H16" s="9"/>
+      <c r="I16" s="27"/>
     </row>
     <row r="17" spans="1:9">
       <c r="A17" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B17" s="7">
-        <v>45870</v>
-      </c>
-      <c r="C17" s="28">
-        <v>45874</v>
-      </c>
-      <c r="D17" s="55">
-        <v>133722984</v>
-      </c>
-      <c r="E17" s="48">
-        <v>3450042464</v>
-      </c>
-      <c r="F17" s="53" t="s">
-        <v>71</v>
-      </c>
-      <c r="G17" s="60" t="s">
-        <v>13</v>
-      </c>
-      <c r="H17" s="59" t="s">
-        <v>58</v>
-      </c>
-      <c r="I17" s="27">
-        <v>45873</v>
-      </c>
+      <c r="B17" s="7"/>
+      <c r="C17" s="28"/>
+      <c r="D17" s="25"/>
+      <c r="E17" s="18"/>
+      <c r="F17" s="12"/>
+      <c r="G17" s="20"/>
+      <c r="H17" s="9"/>
+      <c r="I17" s="27"/>
     </row>
     <row r="18" spans="1:9">
-      <c r="A18" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B18" s="7">
-        <v>45873</v>
-      </c>
-      <c r="C18" s="28">
-        <v>45874</v>
-      </c>
-      <c r="D18" s="55">
-        <v>133762552</v>
-      </c>
-      <c r="E18" s="48">
-        <v>3450044884</v>
-      </c>
-      <c r="F18" s="53" t="s">
-        <v>72</v>
-      </c>
-      <c r="G18" s="60" t="s">
-        <v>21</v>
-      </c>
-      <c r="H18" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="I18" s="27">
-        <v>45873</v>
-      </c>
+      <c r="A18" s="6"/>
+      <c r="B18" s="7"/>
+      <c r="C18" s="28"/>
+      <c r="D18" s="25"/>
+      <c r="E18" s="18"/>
+      <c r="F18" s="12"/>
+      <c r="G18" s="20"/>
+      <c r="H18" s="9"/>
+      <c r="I18" s="27"/>
     </row>
     <row r="19" spans="1:9">
-      <c r="A19" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B19" s="7">
-        <v>45863</v>
-      </c>
-      <c r="C19" s="28">
-        <v>45874</v>
-      </c>
-      <c r="D19" s="55">
-        <v>133572143</v>
-      </c>
-      <c r="E19" s="48">
-        <v>3450035721</v>
-      </c>
-      <c r="F19" s="53" t="s">
-        <v>73</v>
-      </c>
-      <c r="G19" s="60" t="s">
-        <v>74</v>
-      </c>
-      <c r="H19" s="59" t="s">
-        <v>75</v>
-      </c>
-      <c r="I19" s="27">
-        <v>45863</v>
-      </c>
+      <c r="A19" s="6"/>
+      <c r="B19" s="7"/>
+      <c r="C19" s="28"/>
+      <c r="D19" s="25"/>
+      <c r="E19" s="18"/>
+      <c r="F19" s="12"/>
+      <c r="G19" s="20"/>
+      <c r="H19" s="9"/>
+      <c r="I19" s="27"/>
     </row>
     <row r="20" spans="1:9">
-      <c r="A20" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B20" s="7">
-        <v>45882</v>
-      </c>
-      <c r="C20" s="28">
-        <v>45874</v>
-      </c>
-      <c r="D20" s="55">
-        <v>133587069</v>
-      </c>
-      <c r="E20" s="48">
-        <v>3450036370</v>
-      </c>
-      <c r="F20" s="53" t="s">
-        <v>76</v>
-      </c>
-      <c r="G20" s="60" t="s">
-        <v>55</v>
-      </c>
-      <c r="H20" s="59" t="s">
-        <v>77</v>
-      </c>
-      <c r="I20" s="27">
-        <v>45863</v>
-      </c>
+      <c r="A20" s="6"/>
+      <c r="B20" s="7"/>
+      <c r="C20" s="28"/>
+      <c r="D20" s="25"/>
+      <c r="E20" s="18"/>
+      <c r="F20" s="12"/>
+      <c r="G20" s="20"/>
+      <c r="H20" s="9"/>
+      <c r="I20" s="27"/>
     </row>
     <row r="21" spans="1:9">
-      <c r="A21" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B21" s="7">
-        <v>45867</v>
-      </c>
-      <c r="C21" s="28">
-        <v>45874</v>
-      </c>
-      <c r="D21" s="55">
-        <v>133673079</v>
-      </c>
-      <c r="E21" s="48">
-        <v>3450040242</v>
-      </c>
-      <c r="F21" s="53" t="s">
-        <v>78</v>
-      </c>
-      <c r="G21" s="60" t="s">
-        <v>24</v>
-      </c>
-      <c r="H21" s="59" t="s">
-        <v>79</v>
-      </c>
-      <c r="I21" s="27">
-        <v>45867</v>
-      </c>
+      <c r="A21" s="6"/>
+      <c r="B21" s="7"/>
+      <c r="C21" s="28"/>
+      <c r="D21" s="25"/>
+      <c r="E21" s="18"/>
+      <c r="F21" s="12"/>
+      <c r="G21" s="20"/>
+      <c r="H21" s="9"/>
+      <c r="I21" s="27"/>
     </row>
     <row r="22" spans="1:9">
-      <c r="A22" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B22" s="7">
-        <v>45884</v>
-      </c>
-      <c r="C22" s="28">
-        <v>45874</v>
-      </c>
-      <c r="D22" s="55">
-        <v>133664733</v>
-      </c>
-      <c r="E22" s="48">
-        <v>3450039725</v>
-      </c>
-      <c r="F22" s="53" t="s">
-        <v>80</v>
-      </c>
-      <c r="G22" s="60" t="s">
-        <v>13</v>
-      </c>
-      <c r="H22" s="59" t="s">
-        <v>58</v>
-      </c>
-      <c r="I22" s="27">
-        <v>45873</v>
-      </c>
+      <c r="A22" s="6"/>
+      <c r="B22" s="7"/>
+      <c r="C22" s="28"/>
+      <c r="D22" s="25"/>
+      <c r="E22" s="18"/>
+      <c r="F22" s="12"/>
+      <c r="G22" s="20"/>
+      <c r="H22" s="9"/>
+      <c r="I22" s="27"/>
     </row>
     <row r="23" spans="1:9">
-      <c r="A23" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B23" s="7">
-        <v>45865</v>
-      </c>
-      <c r="C23" s="28">
-        <v>45874</v>
-      </c>
-      <c r="D23" s="55">
-        <v>133637794</v>
-      </c>
-      <c r="E23" s="48">
-        <v>3450038537</v>
-      </c>
-      <c r="F23" s="53" t="s">
-        <v>81</v>
-      </c>
-      <c r="G23" s="60" t="s">
-        <v>21</v>
-      </c>
-      <c r="H23" s="31" t="s">
-        <v>22</v>
-      </c>
-      <c r="I23" s="27">
-        <v>45865</v>
-      </c>
+      <c r="A23" s="6"/>
+      <c r="B23" s="7"/>
+      <c r="C23" s="28"/>
+      <c r="D23" s="25"/>
+      <c r="E23" s="18"/>
+      <c r="F23" s="12"/>
+      <c r="G23" s="20"/>
+      <c r="H23" s="9"/>
+      <c r="I23" s="27"/>
     </row>
     <row r="24" spans="1:9">
-      <c r="A24" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B24" s="7">
-        <v>45866</v>
-      </c>
-      <c r="C24" s="28">
-        <v>45874</v>
-      </c>
-      <c r="D24" s="55">
-        <v>133653367</v>
-      </c>
-      <c r="E24" s="48">
-        <v>3450039131</v>
-      </c>
-      <c r="F24" s="53" t="s">
-        <v>82</v>
-      </c>
-      <c r="G24" s="60" t="s">
-        <v>21</v>
-      </c>
-      <c r="H24" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="I24" s="27">
-        <v>45866</v>
-      </c>
+      <c r="A24" s="6"/>
+      <c r="B24" s="7"/>
+      <c r="C24" s="28"/>
+      <c r="D24" s="25"/>
+      <c r="E24" s="18"/>
+      <c r="F24" s="12"/>
+      <c r="G24" s="20"/>
+      <c r="H24" s="9"/>
+      <c r="I24" s="27"/>
     </row>
     <row r="25" spans="1:9">
-      <c r="A25" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B25" s="7">
-        <v>45866</v>
-      </c>
-      <c r="C25" s="28">
-        <v>45874</v>
-      </c>
-      <c r="D25" s="55">
-        <v>133653584</v>
-      </c>
-      <c r="E25" s="48">
-        <v>3450039153</v>
-      </c>
-      <c r="F25" s="53" t="s">
-        <v>83</v>
-      </c>
-      <c r="G25" s="60" t="s">
-        <v>21</v>
-      </c>
-      <c r="H25" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="I25" s="27">
-        <v>45866</v>
-      </c>
+      <c r="A25" s="6"/>
+      <c r="B25" s="7"/>
+      <c r="C25" s="28"/>
+      <c r="D25" s="25"/>
+      <c r="E25" s="18"/>
+      <c r="F25" s="12"/>
+      <c r="G25" s="20"/>
+      <c r="H25" s="9"/>
+      <c r="I25" s="27"/>
     </row>
     <row r="26" spans="1:9">
       <c r="A26" s="6"/>
       <c r="B26" s="7"/>
       <c r="C26" s="28"/>
-      <c r="D26" s="51"/>
-      <c r="E26" s="54"/>
-      <c r="F26" s="35"/>
-      <c r="G26" s="60"/>
-      <c r="H26" s="9"/>
+      <c r="D26" s="25"/>
+      <c r="E26" s="18"/>
+      <c r="F26" s="12"/>
+      <c r="G26" s="20"/>
+      <c r="H26" s="32"/>
       <c r="I26" s="27"/>
     </row>
     <row r="27" spans="1:9">
@@ -2934,7 +2350,7 @@
       <c r="D27" s="25"/>
       <c r="E27" s="18"/>
       <c r="F27" s="12"/>
-      <c r="G27" s="60"/>
+      <c r="G27" s="20"/>
       <c r="H27" s="9"/>
       <c r="I27" s="27"/>
     </row>
@@ -2945,7 +2361,7 @@
       <c r="D28" s="25"/>
       <c r="E28" s="18"/>
       <c r="F28" s="12"/>
-      <c r="G28" s="60"/>
+      <c r="G28" s="20"/>
       <c r="H28" s="9"/>
       <c r="I28" s="27"/>
     </row>
@@ -2956,7 +2372,7 @@
       <c r="D29" s="25"/>
       <c r="E29" s="18"/>
       <c r="F29" s="12"/>
-      <c r="G29" s="60"/>
+      <c r="G29" s="20"/>
       <c r="H29" s="9"/>
       <c r="I29" s="27"/>
     </row>
@@ -2967,40 +2383,40 @@
       <c r="D30" s="25"/>
       <c r="E30" s="18"/>
       <c r="F30" s="12"/>
-      <c r="G30" s="60"/>
+      <c r="G30" s="20"/>
       <c r="H30" s="9"/>
       <c r="I30" s="27"/>
     </row>
     <row r="31" spans="1:9">
       <c r="A31" s="6"/>
-      <c r="B31" s="8"/>
-      <c r="C31" s="7"/>
-      <c r="D31" s="23"/>
-      <c r="E31" s="23"/>
-      <c r="F31" s="15"/>
-      <c r="G31" s="62"/>
+      <c r="B31" s="7"/>
+      <c r="C31" s="28"/>
+      <c r="D31" s="25"/>
+      <c r="E31" s="18"/>
+      <c r="F31" s="12"/>
+      <c r="G31" s="20"/>
       <c r="H31" s="9"/>
       <c r="I31" s="27"/>
     </row>
     <row r="32" spans="1:9">
       <c r="A32" s="6"/>
-      <c r="B32" s="8"/>
-      <c r="C32" s="7"/>
-      <c r="D32" s="8"/>
-      <c r="E32" s="8"/>
-      <c r="F32" s="9"/>
-      <c r="G32" s="62"/>
+      <c r="B32" s="7"/>
+      <c r="C32" s="28"/>
+      <c r="D32" s="25"/>
+      <c r="E32" s="18"/>
+      <c r="F32" s="12"/>
+      <c r="G32" s="20"/>
       <c r="H32" s="9"/>
       <c r="I32" s="27"/>
     </row>
     <row r="33" spans="1:9">
       <c r="A33" s="6"/>
-      <c r="B33" s="8"/>
-      <c r="C33" s="7"/>
-      <c r="D33" s="8"/>
-      <c r="E33" s="8"/>
-      <c r="F33" s="9"/>
-      <c r="G33" s="62"/>
+      <c r="B33" s="7"/>
+      <c r="C33" s="28"/>
+      <c r="D33" s="25"/>
+      <c r="E33" s="18"/>
+      <c r="F33" s="12"/>
+      <c r="G33" s="20"/>
       <c r="H33" s="9"/>
       <c r="I33" s="27"/>
     </row>
@@ -3008,12 +2424,12 @@
       <c r="A34" s="6"/>
       <c r="B34" s="8"/>
       <c r="C34" s="7"/>
-      <c r="D34" s="8"/>
-      <c r="E34" s="8"/>
-      <c r="F34" s="9"/>
-      <c r="G34" s="62"/>
+      <c r="D34" s="23"/>
+      <c r="E34" s="23"/>
+      <c r="F34" s="15"/>
+      <c r="G34" s="6"/>
       <c r="H34" s="9"/>
-      <c r="I34"/>
+      <c r="I34" s="27"/>
     </row>
     <row r="35" spans="1:9">
       <c r="A35" s="6"/>
@@ -3022,9 +2438,9 @@
       <c r="D35" s="8"/>
       <c r="E35" s="8"/>
       <c r="F35" s="9"/>
-      <c r="G35" s="62"/>
+      <c r="G35" s="6"/>
       <c r="H35" s="9"/>
-      <c r="I35"/>
+      <c r="I35" s="27"/>
     </row>
     <row r="36" spans="1:9">
       <c r="A36" s="6"/>
@@ -3033,9 +2449,9 @@
       <c r="D36" s="8"/>
       <c r="E36" s="8"/>
       <c r="F36" s="9"/>
-      <c r="G36" s="62"/>
+      <c r="G36" s="6"/>
       <c r="H36" s="9"/>
-      <c r="I36"/>
+      <c r="I36" s="27"/>
     </row>
     <row r="37" spans="1:9">
       <c r="A37" s="6"/>
@@ -3044,7 +2460,7 @@
       <c r="D37" s="8"/>
       <c r="E37" s="8"/>
       <c r="F37" s="9"/>
-      <c r="G37" s="62"/>
+      <c r="G37" s="6"/>
       <c r="H37" s="9"/>
       <c r="I37"/>
     </row>
@@ -3055,7 +2471,7 @@
       <c r="D38" s="8"/>
       <c r="E38" s="8"/>
       <c r="F38" s="9"/>
-      <c r="G38" s="62"/>
+      <c r="G38" s="6"/>
       <c r="H38" s="9"/>
       <c r="I38"/>
     </row>
@@ -3066,7 +2482,7 @@
       <c r="D39" s="8"/>
       <c r="E39" s="8"/>
       <c r="F39" s="9"/>
-      <c r="G39" s="62"/>
+      <c r="G39" s="6"/>
       <c r="H39" s="9"/>
       <c r="I39"/>
     </row>
@@ -3077,7 +2493,7 @@
       <c r="D40" s="8"/>
       <c r="E40" s="8"/>
       <c r="F40" s="9"/>
-      <c r="G40" s="62"/>
+      <c r="G40" s="6"/>
       <c r="H40" s="9"/>
       <c r="I40"/>
     </row>
@@ -3088,7 +2504,7 @@
       <c r="D41" s="8"/>
       <c r="E41" s="8"/>
       <c r="F41" s="9"/>
-      <c r="G41" s="62"/>
+      <c r="G41" s="6"/>
       <c r="H41" s="9"/>
       <c r="I41"/>
     </row>
@@ -3099,7 +2515,7 @@
       <c r="D42" s="8"/>
       <c r="E42" s="8"/>
       <c r="F42" s="9"/>
-      <c r="G42" s="62"/>
+      <c r="G42" s="6"/>
       <c r="H42" s="9"/>
       <c r="I42"/>
     </row>
@@ -3110,7 +2526,7 @@
       <c r="D43" s="8"/>
       <c r="E43" s="8"/>
       <c r="F43" s="9"/>
-      <c r="G43" s="62"/>
+      <c r="G43" s="6"/>
       <c r="H43" s="9"/>
       <c r="I43"/>
     </row>
@@ -3121,7 +2537,7 @@
       <c r="D44" s="8"/>
       <c r="E44" s="8"/>
       <c r="F44" s="9"/>
-      <c r="G44" s="62"/>
+      <c r="G44" s="6"/>
       <c r="H44" s="9"/>
       <c r="I44"/>
     </row>
@@ -3132,7 +2548,7 @@
       <c r="D45" s="8"/>
       <c r="E45" s="8"/>
       <c r="F45" s="9"/>
-      <c r="G45" s="62"/>
+      <c r="G45" s="6"/>
       <c r="H45" s="9"/>
       <c r="I45"/>
     </row>
@@ -3143,7 +2559,7 @@
       <c r="D46" s="8"/>
       <c r="E46" s="8"/>
       <c r="F46" s="9"/>
-      <c r="G46" s="62"/>
+      <c r="G46" s="6"/>
       <c r="H46" s="9"/>
       <c r="I46"/>
     </row>
@@ -3154,7 +2570,7 @@
       <c r="D47" s="8"/>
       <c r="E47" s="8"/>
       <c r="F47" s="9"/>
-      <c r="G47" s="62"/>
+      <c r="G47" s="6"/>
       <c r="H47" s="9"/>
       <c r="I47"/>
     </row>
@@ -3165,7 +2581,7 @@
       <c r="D48" s="8"/>
       <c r="E48" s="8"/>
       <c r="F48" s="9"/>
-      <c r="G48" s="62"/>
+      <c r="G48" s="6"/>
       <c r="H48" s="9"/>
       <c r="I48"/>
     </row>
@@ -3176,7 +2592,7 @@
       <c r="D49" s="8"/>
       <c r="E49" s="8"/>
       <c r="F49" s="9"/>
-      <c r="G49" s="62"/>
+      <c r="G49" s="6"/>
       <c r="H49" s="9"/>
       <c r="I49"/>
     </row>
@@ -3187,7 +2603,7 @@
       <c r="D50" s="8"/>
       <c r="E50" s="8"/>
       <c r="F50" s="9"/>
-      <c r="G50" s="62"/>
+      <c r="G50" s="6"/>
       <c r="H50" s="9"/>
       <c r="I50"/>
     </row>
@@ -3198,7 +2614,7 @@
       <c r="D51" s="8"/>
       <c r="E51" s="8"/>
       <c r="F51" s="9"/>
-      <c r="G51" s="62"/>
+      <c r="G51" s="6"/>
       <c r="H51" s="9"/>
       <c r="I51"/>
     </row>
@@ -3209,27 +2625,54 @@
       <c r="D52" s="8"/>
       <c r="E52" s="8"/>
       <c r="F52" s="9"/>
-      <c r="G52" s="62"/>
+      <c r="G52" s="6"/>
       <c r="H52" s="9"/>
       <c r="I52"/>
     </row>
+    <row r="53" spans="1:9">
+      <c r="A53" s="6"/>
+      <c r="B53" s="8"/>
+      <c r="C53" s="7"/>
+      <c r="D53" s="8"/>
+      <c r="E53" s="8"/>
+      <c r="F53" s="9"/>
+      <c r="G53" s="6"/>
+      <c r="H53" s="9"/>
+      <c r="I53"/>
+    </row>
+    <row r="54" spans="1:9">
+      <c r="A54" s="6"/>
+      <c r="B54" s="8"/>
+      <c r="C54" s="7"/>
+      <c r="D54" s="8"/>
+      <c r="E54" s="8"/>
+      <c r="F54" s="9"/>
+      <c r="G54" s="6"/>
+      <c r="H54" s="9"/>
+      <c r="I54"/>
+    </row>
+    <row r="55" spans="1:9">
+      <c r="A55" s="6"/>
+      <c r="B55" s="8"/>
+      <c r="C55" s="7"/>
+      <c r="D55" s="8"/>
+      <c r="E55" s="8"/>
+      <c r="F55" s="9"/>
+      <c r="G55" s="6"/>
+      <c r="H55" s="9"/>
+      <c r="I55"/>
+    </row>
   </sheetData>
   <conditionalFormatting sqref="B1:C1">
-    <cfRule type="notContainsBlanks" priority="5">
+    <cfRule type="notContainsBlanks" priority="2">
       <formula>LEN(TRIM(B1))&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2">
-    <cfRule type="duplicateValues" dxfId="1" priority="3"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E3">
-    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
-  </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2:A30" xr:uid="{4D257AA8-3FDB-42B7-A450-B3788B0ABB12}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2:A33" xr:uid="{4D257AA8-3FDB-42B7-A450-B3788B0ABB12}">
       <formula1>$J$2</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G38" xr:uid="{5FAA0C61-6912-46B8-8149-B719594B77CB}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G41" xr:uid="{5FAA0C61-6912-46B8-8149-B719594B77CB}">
       <formula1>"Vistoria Frustrada;,Vistoria Recusada,Bônus;,Desistência;,Inadimplência;,Política de Aceitação;,Duplicidade;,Demais Motivos,Falta de Vistoria;,"</formula1>
     </dataValidation>
   </dataValidations>
@@ -3277,7 +2720,7 @@
       <c r="H1" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="32" t="s">
+      <c r="I1" s="33" t="s">
         <v>8</v>
       </c>
     </row>
@@ -4440,7 +3883,7 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="43" t="s">
+      <c r="H1" s="44" t="s">
         <v>7</v>
       </c>
       <c r="I1" s="5" t="s">
@@ -4453,11 +3896,11 @@
       </c>
       <c r="B2" s="7"/>
       <c r="C2" s="28"/>
-      <c r="D2" s="46"/>
+      <c r="D2" s="47"/>
       <c r="E2" s="18"/>
       <c r="F2" s="19"/>
-      <c r="G2" s="41"/>
-      <c r="H2" s="38"/>
+      <c r="G2" s="42"/>
+      <c r="H2" s="39"/>
       <c r="I2" s="27"/>
     </row>
     <row r="3" spans="1:9">
@@ -4469,8 +3912,8 @@
       <c r="D3" s="25"/>
       <c r="E3" s="18"/>
       <c r="F3" s="19"/>
-      <c r="G3" s="41"/>
-      <c r="H3" s="38"/>
+      <c r="G3" s="42"/>
+      <c r="H3" s="39"/>
       <c r="I3" s="27"/>
     </row>
     <row r="4" spans="1:9">
@@ -4482,8 +3925,8 @@
       <c r="D4" s="25"/>
       <c r="E4" s="18"/>
       <c r="F4" s="19"/>
-      <c r="G4" s="41"/>
-      <c r="H4" s="38"/>
+      <c r="G4" s="42"/>
+      <c r="H4" s="39"/>
       <c r="I4" s="27"/>
     </row>
     <row r="5" spans="1:9">
@@ -4495,8 +3938,8 @@
       <c r="D5" s="25"/>
       <c r="E5" s="18"/>
       <c r="F5" s="19"/>
-      <c r="G5" s="41"/>
-      <c r="H5" s="39"/>
+      <c r="G5" s="42"/>
+      <c r="H5" s="40"/>
       <c r="I5" s="27"/>
     </row>
     <row r="6" spans="1:9">
@@ -4508,8 +3951,8 @@
       <c r="D6" s="25"/>
       <c r="E6" s="18"/>
       <c r="F6" s="19"/>
-      <c r="G6" s="42"/>
-      <c r="H6" s="40"/>
+      <c r="G6" s="43"/>
+      <c r="H6" s="41"/>
       <c r="I6" s="27"/>
     </row>
     <row r="7" spans="1:9">
@@ -4521,8 +3964,8 @@
       <c r="D7" s="25"/>
       <c r="E7" s="18"/>
       <c r="F7" s="19"/>
-      <c r="G7" s="44"/>
-      <c r="H7" s="40"/>
+      <c r="G7" s="45"/>
+      <c r="H7" s="41"/>
       <c r="I7" s="27"/>
     </row>
     <row r="8" spans="1:9">
@@ -4534,8 +3977,8 @@
       <c r="D8" s="25"/>
       <c r="E8" s="18"/>
       <c r="F8" s="19"/>
-      <c r="G8" s="45"/>
-      <c r="H8" s="40"/>
+      <c r="G8" s="46"/>
+      <c r="H8" s="41"/>
       <c r="I8" s="27"/>
     </row>
     <row r="9" spans="1:9">
@@ -4547,8 +3990,8 @@
       <c r="D9" s="25"/>
       <c r="E9" s="18"/>
       <c r="F9" s="19"/>
-      <c r="G9" s="45"/>
-      <c r="H9" s="38"/>
+      <c r="G9" s="46"/>
+      <c r="H9" s="39"/>
       <c r="I9" s="27"/>
     </row>
     <row r="10" spans="1:9">
@@ -4560,8 +4003,8 @@
       <c r="D10" s="25"/>
       <c r="E10" s="18"/>
       <c r="F10" s="19"/>
-      <c r="G10" s="45"/>
-      <c r="H10" s="38"/>
+      <c r="G10" s="46"/>
+      <c r="H10" s="39"/>
       <c r="I10" s="27"/>
     </row>
     <row r="11" spans="1:9">
@@ -4573,8 +4016,8 @@
       <c r="D11" s="25"/>
       <c r="E11" s="18"/>
       <c r="F11" s="19"/>
-      <c r="G11" s="45"/>
-      <c r="H11" s="38"/>
+      <c r="G11" s="46"/>
+      <c r="H11" s="39"/>
       <c r="I11" s="27"/>
     </row>
     <row r="12" spans="1:9">
@@ -4586,8 +4029,8 @@
       <c r="D12" s="25"/>
       <c r="E12" s="18"/>
       <c r="F12" s="19"/>
-      <c r="G12" s="45"/>
-      <c r="H12" s="38"/>
+      <c r="G12" s="46"/>
+      <c r="H12" s="39"/>
       <c r="I12" s="27"/>
     </row>
     <row r="13" spans="1:9">
@@ -4599,8 +4042,8 @@
       <c r="D13" s="25"/>
       <c r="E13" s="18"/>
       <c r="F13" s="19"/>
-      <c r="G13" s="45"/>
-      <c r="H13" s="38"/>
+      <c r="G13" s="46"/>
+      <c r="H13" s="39"/>
       <c r="I13" s="27"/>
     </row>
     <row r="14" spans="1:9">
@@ -4612,8 +4055,8 @@
       <c r="D14" s="25"/>
       <c r="E14" s="18"/>
       <c r="F14" s="19"/>
-      <c r="G14" s="45"/>
-      <c r="H14" s="38"/>
+      <c r="G14" s="46"/>
+      <c r="H14" s="39"/>
       <c r="I14" s="27"/>
     </row>
     <row r="15" spans="1:9">
@@ -4625,8 +4068,8 @@
       <c r="D15" s="25"/>
       <c r="E15" s="18"/>
       <c r="F15" s="19"/>
-      <c r="G15" s="45"/>
-      <c r="H15" s="38"/>
+      <c r="G15" s="46"/>
+      <c r="H15" s="39"/>
       <c r="I15" s="27"/>
     </row>
     <row r="16" spans="1:9">
@@ -4638,8 +4081,8 @@
       <c r="D16" s="25"/>
       <c r="E16" s="18"/>
       <c r="F16" s="12"/>
-      <c r="G16" s="45"/>
-      <c r="H16" s="38"/>
+      <c r="G16" s="46"/>
+      <c r="H16" s="39"/>
       <c r="I16" s="27"/>
     </row>
     <row r="17" spans="1:9" ht="15" customHeight="1">
@@ -4651,8 +4094,8 @@
       <c r="D17" s="25"/>
       <c r="E17" s="18"/>
       <c r="F17" s="12"/>
-      <c r="G17" s="41"/>
-      <c r="H17" s="38"/>
+      <c r="G17" s="42"/>
+      <c r="H17" s="39"/>
       <c r="I17" s="27"/>
     </row>
     <row r="18" spans="1:9">
@@ -4664,8 +4107,8 @@
       <c r="D18" s="25"/>
       <c r="E18" s="18"/>
       <c r="F18" s="12"/>
-      <c r="G18" s="45"/>
-      <c r="H18" s="38"/>
+      <c r="G18" s="46"/>
+      <c r="H18" s="39"/>
       <c r="I18" s="27"/>
     </row>
     <row r="19" spans="1:9">
@@ -4673,9 +4116,9 @@
       <c r="B19" s="8"/>
       <c r="C19" s="7"/>
       <c r="D19" s="23"/>
-      <c r="E19" s="34"/>
-      <c r="F19" s="36"/>
-      <c r="G19" s="33"/>
+      <c r="E19" s="35"/>
+      <c r="F19" s="37"/>
+      <c r="G19" s="34"/>
       <c r="H19" s="9"/>
       <c r="I19" s="27"/>
     </row>
@@ -4686,7 +4129,7 @@
       <c r="D20" s="8"/>
       <c r="E20" s="8"/>
       <c r="F20" s="15"/>
-      <c r="G20" s="33"/>
+      <c r="G20" s="34"/>
       <c r="H20" s="9"/>
       <c r="I20" s="27"/>
     </row>
@@ -4697,7 +4140,7 @@
       <c r="D21" s="8"/>
       <c r="E21" s="8"/>
       <c r="F21" s="9"/>
-      <c r="G21" s="33"/>
+      <c r="G21" s="34"/>
       <c r="H21" s="9"/>
       <c r="I21" s="27"/>
     </row>
@@ -4708,7 +4151,7 @@
       <c r="D22" s="8"/>
       <c r="E22" s="8"/>
       <c r="F22" s="9"/>
-      <c r="G22" s="33"/>
+      <c r="G22" s="34"/>
       <c r="H22" s="9"/>
       <c r="I22" s="27"/>
     </row>
@@ -4719,7 +4162,7 @@
       <c r="D23" s="8"/>
       <c r="E23" s="8"/>
       <c r="F23" s="9"/>
-      <c r="G23" s="33"/>
+      <c r="G23" s="34"/>
       <c r="H23" s="9"/>
       <c r="I23" s="27"/>
     </row>
@@ -4730,7 +4173,7 @@
       <c r="D24" s="8"/>
       <c r="E24" s="8"/>
       <c r="F24" s="9"/>
-      <c r="G24" s="33"/>
+      <c r="G24" s="34"/>
       <c r="H24" s="9"/>
       <c r="I24" s="27"/>
     </row>
@@ -5161,7 +4604,7 @@
       <c r="F3" s="12"/>
       <c r="G3" s="20"/>
       <c r="H3" s="9"/>
-      <c r="I3" s="37"/>
+      <c r="I3" s="38"/>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="6" t="s">
@@ -5194,8 +4637,8 @@
       <c r="B6" s="7"/>
       <c r="C6" s="7"/>
       <c r="D6" s="23"/>
-      <c r="E6" s="34"/>
-      <c r="F6" s="35"/>
+      <c r="E6" s="35"/>
+      <c r="F6" s="36"/>
       <c r="G6" s="6"/>
       <c r="H6" s="9"/>
       <c r="I6" s="27"/>
@@ -6352,60 +5795,8 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_dlc_DocId xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">QAFFA7D2F2TC-2102087286-494890</_dlc_DocId>
-    <_dlc_DocIdUrl xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">
-      <Url>https://allianzms.sharepoint.com/teams/BR0010-4356589/_layouts/15/DocIdRedir.aspx?ID=QAFFA7D2F2TC-2102087286-494890</Url>
-      <Description>QAFFA7D2F2TC-2102087286-494890</Description>
-    </_dlc_DocIdUrl>
-    <DossierOwner xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </DossierOwner>
-    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <ccca9d190a3c43e89f73773ee806c8b5 xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </ccca9d190a3c43e89f73773ee806c8b5>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="ea6c6725-5210-4d6a-93cc-4cf85111ac5e">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <ContractDate xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
-    <MailPreviewData xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
-    <_Flow_SignoffStatus xmlns="ea6c6725-5210-4d6a-93cc-4cf85111ac5e" xsi:nil="true"/>
-    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <ContractExpirationDate xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
-    <DossierStatus xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
-    <ia4b831ccad64069ad2e0cbd870e9b8a xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </ia4b831ccad64069ad2e0cbd870e9b8a>
-    <TaxCatchAll xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
-    <alteradopor xmlns="ea6c6725-5210-4d6a-93cc-4cf85111ac5e">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </alteradopor>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x01010006E7B04763359F4AAB0FC84D5027BFC8" ma:contentTypeVersion="43" ma:contentTypeDescription="Criar um novo documento." ma:contentTypeScope="" ma:versionID="32fbec5585ae01a22f32af5838af0c4d">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xmlns:ns3="ea6c6725-5210-4d6a-93cc-4cf85111ac5e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="7b2552458edfdc024ce707f91c2c891f" ns1:_="" ns2:_="" ns3:_="">
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010006E7B04763359F4AAB0FC84D5027BFC8" ma:contentTypeVersion="43" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="abf1b9912853fe4a934dbc2373304754">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xmlns:ns3="ea6c6725-5210-4d6a-93cc-4cf85111ac5e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="d8d96f03b10d24171ef462918d18284e" ns1:_="" ns2:_="" ns3:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
     <xsd:import namespace="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea"/>
     <xsd:import namespace="ea6c6725-5210-4d6a-93cc-4cf85111ac5e"/>
@@ -6453,12 +5844,12 @@
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="http://schemas.microsoft.com/sharepoint/v3" elementFormDefault="qualified">
     <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
     <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="_ip_UnifiedCompliancePolicyProperties" ma:index="23" nillable="true" ma:displayName="Propriedades da Política de Conformidade Unificada" ma:hidden="true" ma:internalName="_ip_UnifiedCompliancePolicyProperties">
+    <xsd:element name="_ip_UnifiedCompliancePolicyProperties" ma:index="23" nillable="true" ma:displayName="Unified Compliance Policy Properties" ma:hidden="true" ma:internalName="_ip_UnifiedCompliancePolicyProperties">
       <xsd:simpleType>
         <xsd:restriction base="dms:Note"/>
       </xsd:simpleType>
     </xsd:element>
-    <xsd:element name="_ip_UnifiedCompliancePolicyUIAction" ma:index="24" nillable="true" ma:displayName="Ação de IU da Política de Conformidade Unificada" ma:hidden="true" ma:internalName="_ip_UnifiedCompliancePolicyUIAction">
+    <xsd:element name="_ip_UnifiedCompliancePolicyUIAction" ma:index="24" nillable="true" ma:displayName="Unified Compliance Policy UI Action" ma:hidden="true" ma:internalName="_ip_UnifiedCompliancePolicyUIAction">
       <xsd:simpleType>
         <xsd:restriction base="dms:Text"/>
       </xsd:simpleType>
@@ -6467,12 +5858,12 @@
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" elementFormDefault="qualified">
     <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
     <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="_dlc_DocId" ma:index="8" nillable="true" ma:displayName="Valor do ID do Documento" ma:description="O valor do ID do documento atribuído a este item." ma:indexed="true" ma:internalName="_dlc_DocId" ma:readOnly="true">
+    <xsd:element name="_dlc_DocId" ma:index="8" nillable="true" ma:displayName="Document ID Value" ma:description="The value of the document ID assigned to this item." ma:indexed="true" ma:internalName="_dlc_DocId" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Text"/>
       </xsd:simpleType>
     </xsd:element>
-    <xsd:element name="_dlc_DocIdUrl" ma:index="9" nillable="true" ma:displayName="ID do Documento" ma:description="Ligação permanente a este documento." ma:hidden="true" ma:internalName="_dlc_DocIdUrl" ma:readOnly="true">
+    <xsd:element name="_dlc_DocIdUrl" ma:index="9" nillable="true" ma:displayName="Document ID" ma:description="Permanent link to this document." ma:hidden="true" ma:internalName="_dlc_DocIdUrl" ma:readOnly="true">
       <xsd:complexType>
         <xsd:complexContent>
           <xsd:extension base="dms:URL">
@@ -6555,7 +5946,7 @@
         <xsd:restriction base="dms:DateTime"/>
       </xsd:simpleType>
     </xsd:element>
-    <xsd:element name="SharedWithUsers" ma:index="19" nillable="true" ma:displayName="Partilhado Com" ma:internalName="SharedWithUsers" ma:readOnly="true">
+    <xsd:element name="SharedWithUsers" ma:index="19" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
       <xsd:complexType>
         <xsd:complexContent>
           <xsd:extension base="dms:UserMulti">
@@ -6574,7 +5965,7 @@
         </xsd:complexContent>
       </xsd:complexType>
     </xsd:element>
-    <xsd:element name="SharedWithDetails" ma:index="20" nillable="true" ma:displayName="Detalhes de Partilhado Com" ma:internalName="SharedWithDetails" ma:readOnly="true">
+    <xsd:element name="SharedWithDetails" ma:index="20" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Note">
           <xsd:maxLength value="255"/>
@@ -6607,7 +5998,7 @@
         <xsd:restriction base="dms:Note"/>
       </xsd:simpleType>
     </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="26" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Etiquetas de Imagem" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="10820af1-e82f-496e-bbcb-d9502914b7b2" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="26" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="10820af1-e82f-496e-bbcb-d9502914b7b2" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
       <xsd:complexType>
         <xsd:sequence>
           <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
@@ -6685,8 +6076,8 @@
         <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
         <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
         <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Tipo de Conteúdo"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Título"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
         <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
         <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
         <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
@@ -6775,6 +6166,58 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_dlc_DocId xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">QAFFA7D2F2TC-2102087286-494890</_dlc_DocId>
+    <_dlc_DocIdUrl xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">
+      <Url>https://allianzms.sharepoint.com/teams/BR0010-4356589/_layouts/15/DocIdRedir.aspx?ID=QAFFA7D2F2TC-2102087286-494890</Url>
+      <Description>QAFFA7D2F2TC-2102087286-494890</Description>
+    </_dlc_DocIdUrl>
+    <DossierOwner xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </DossierOwner>
+    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <ccca9d190a3c43e89f73773ee806c8b5 xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </ccca9d190a3c43e89f73773ee806c8b5>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="ea6c6725-5210-4d6a-93cc-4cf85111ac5e">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <ContractDate xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
+    <MailPreviewData xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
+    <_Flow_SignoffStatus xmlns="ea6c6725-5210-4d6a-93cc-4cf85111ac5e" xsi:nil="true"/>
+    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <ContractExpirationDate xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
+    <DossierStatus xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
+    <ia4b831ccad64069ad2e0cbd870e9b8a xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </ia4b831ccad64069ad2e0cbd870e9b8a>
+    <TaxCatchAll xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
+    <alteradopor xmlns="ea6c6725-5210-4d6a-93cc-4cf85111ac5e">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </alteradopor>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <spe:Receivers xmlns:spe="http://schemas.microsoft.com/sharepoint/events">
@@ -6826,7 +6269,7 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BC9CB02D-0F63-4CE2-B316-61A87327416C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{52D5A726-16FA-4932-8BF5-855F9B379AB9}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -6834,7 +6277,7 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{11932F8B-2F43-467F-BFC3-DB084CEB998D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BC9CB02D-0F63-4CE2-B316-61A87327416C}"/>
 </file>
 
 <file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
